--- a/artfynd/A 13525-2026 artfynd.xlsx
+++ b/artfynd/A 13525-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1345,6 +1345,4859 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132197619</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79895</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>411038</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6710225</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132197630</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79895</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>410994</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6710184</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132197648</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>410933</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6710072</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132197640</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79362</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>410985</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6710205</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132197663</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78942</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>353</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>410929</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6710058</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132197666</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78942</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>353</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>410952</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6710169</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132197601</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79895</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>410984</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6709997</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132197669</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78942</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>353</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>410992</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6710219</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132197643</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79300</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>410998</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6710163</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132197635</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79895</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>410936</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6710017</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132197665</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78942</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>353</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>410902</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6710163</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132197671</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78942</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>353</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>410977</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6710177</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132197670</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78942</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>353</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>410995</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6710181</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132197631</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79895</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>410991</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6710191</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132197633</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79895</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>410961</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6710167</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132197608</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79895</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>410931</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6710096</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132197651</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>411000</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6710007</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132197652</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>410937</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6710017</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132197654</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79033</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>410960</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6710167</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132197602</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79895</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>410973</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6709995</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132197636</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79895</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>410907</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6710026</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132197644</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79300</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>410908</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6710026</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132197637</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79866</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>410906</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6710027</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132197615</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79895</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>410939</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6710183</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132197605</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79895</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>410950</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6709984</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>132197647</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>410950</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6709984</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>132197667</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78942</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>353</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>411027</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6710222</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>132197655</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79033</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>411091</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6710283</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>132197653</v>
+      </c>
+      <c r="B36" t="n">
+        <v>81261</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>410972</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6710194</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>132197646</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>410983</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6709997</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>132197659</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78942</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>353</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>410973</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6709994</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>132197650</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>410986</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6710178</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>132197618</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79895</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>411027</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6710222</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>132197634</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79895</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>410980</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6710008</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>132197632</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79895</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>410998</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6710163</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>132197600</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78942</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>353</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>410935</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6710081</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>132197609</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79895</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>410902</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6710163</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>132197656</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79276</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>410938</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6710077</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>132197662</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78942</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>353</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>410939</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6710046</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>132197606</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79895</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>410946</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6709981</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>132197627</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79895</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>410971</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6710196</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>132197668</v>
+      </c>
+      <c r="B49" t="n">
+        <v>78942</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>353</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>411097</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6710289</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>132197628</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79895</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>410998</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6710174</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>132197629</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79895</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>410993</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6710175</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>132197604</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79895</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>410959</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6709986</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>132197661</v>
+      </c>
+      <c r="B53" t="n">
+        <v>78942</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>353</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>410984</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6709996</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>132197660</v>
+      </c>
+      <c r="B54" t="n">
+        <v>78942</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>353</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>410994</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6710185</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>132197616</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79895</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>410952</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6710170</v>
+      </c>
+      <c r="S55" t="n">
+        <v>25</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>132197664</v>
+      </c>
+      <c r="B56" t="n">
+        <v>78942</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>353</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>410928</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6710090</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>132197607</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79895</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>410933</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6710072</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13525-2026 artfynd.xlsx
+++ b/artfynd/A 13525-2026 artfynd.xlsx
@@ -1347,32 +1347,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132197619</v>
+        <v>132197640</v>
       </c>
       <c r="B8" t="n">
-        <v>79895</v>
+        <v>79362</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6450</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>411038</v>
+        <v>410985</v>
       </c>
       <c r="R8" t="n">
-        <v>6710225</v>
+        <v>6710205</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1444,7 +1444,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132197630</v>
+        <v>132197619</v>
       </c>
       <c r="B9" t="n">
         <v>79895</v>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>410994</v>
+        <v>411038</v>
       </c>
       <c r="R9" t="n">
-        <v>6710184</v>
+        <v>6710225</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1638,32 +1638,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132197640</v>
+        <v>132197630</v>
       </c>
       <c r="B11" t="n">
-        <v>79362</v>
+        <v>79895</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410985</v>
+        <v>410994</v>
       </c>
       <c r="R11" t="n">
-        <v>6710205</v>
+        <v>6710184</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1832,7 +1832,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132197666</v>
+        <v>132197669</v>
       </c>
       <c r="B13" t="n">
         <v>78942</v>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>410952</v>
+        <v>410992</v>
       </c>
       <c r="R13" t="n">
-        <v>6710169</v>
+        <v>6710219</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132197601</v>
+        <v>132197666</v>
       </c>
       <c r="B14" t="n">
-        <v>79895</v>
+        <v>78942</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1940,21 +1940,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>410984</v>
+        <v>410952</v>
       </c>
       <c r="R14" t="n">
-        <v>6709997</v>
+        <v>6710169</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2026,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132197669</v>
+        <v>132197601</v>
       </c>
       <c r="B15" t="n">
-        <v>78942</v>
+        <v>79895</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>410992</v>
+        <v>410984</v>
       </c>
       <c r="R15" t="n">
-        <v>6710219</v>
+        <v>6709997</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2414,7 +2414,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132197671</v>
+        <v>132197670</v>
       </c>
       <c r="B19" t="n">
         <v>78942</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>410977</v>
+        <v>410995</v>
       </c>
       <c r="R19" t="n">
-        <v>6710177</v>
+        <v>6710181</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132197670</v>
+        <v>132197671</v>
       </c>
       <c r="B20" t="n">
         <v>78942</v>
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>410995</v>
+        <v>410977</v>
       </c>
       <c r="R20" t="n">
-        <v>6710181</v>
+        <v>6710177</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2608,7 +2608,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132197631</v>
+        <v>132197633</v>
       </c>
       <c r="B21" t="n">
         <v>79895</v>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>410991</v>
+        <v>410961</v>
       </c>
       <c r="R21" t="n">
-        <v>6710191</v>
+        <v>6710167</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2705,10 +2705,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132197633</v>
+        <v>132197652</v>
       </c>
       <c r="B22" t="n">
-        <v>79895</v>
+        <v>79034</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2716,21 +2716,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>410961</v>
+        <v>410937</v>
       </c>
       <c r="R22" t="n">
-        <v>6710167</v>
+        <v>6710017</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2802,7 +2802,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132197608</v>
+        <v>132197631</v>
       </c>
       <c r="B23" t="n">
         <v>79895</v>
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410931</v>
+        <v>410991</v>
       </c>
       <c r="R23" t="n">
-        <v>6710096</v>
+        <v>6710191</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132197651</v>
+        <v>132197608</v>
       </c>
       <c r="B24" t="n">
-        <v>79034</v>
+        <v>79895</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2910,21 +2910,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>411000</v>
+        <v>410931</v>
       </c>
       <c r="R24" t="n">
-        <v>6710007</v>
+        <v>6710096</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2996,7 +2996,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132197652</v>
+        <v>132197651</v>
       </c>
       <c r="B25" t="n">
         <v>79034</v>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410937</v>
+        <v>411000</v>
       </c>
       <c r="R25" t="n">
-        <v>6710017</v>
+        <v>6710007</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3287,32 +3287,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132197636</v>
+        <v>132197644</v>
       </c>
       <c r="B28" t="n">
-        <v>79895</v>
+        <v>79300</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>410907</v>
+        <v>410908</v>
       </c>
       <c r="R28" t="n">
         <v>6710026</v>
@@ -3384,32 +3384,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132197644</v>
+        <v>132197636</v>
       </c>
       <c r="B29" t="n">
-        <v>79300</v>
+        <v>79895</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>410908</v>
+        <v>410907</v>
       </c>
       <c r="R29" t="n">
         <v>6710026</v>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132197615</v>
+        <v>132197647</v>
       </c>
       <c r="B31" t="n">
-        <v>79895</v>
+        <v>79034</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>410939</v>
+        <v>410950</v>
       </c>
       <c r="R31" t="n">
-        <v>6710183</v>
+        <v>6709984</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132197605</v>
+        <v>132197667</v>
       </c>
       <c r="B32" t="n">
-        <v>79895</v>
+        <v>78942</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3686,21 +3686,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>410950</v>
+        <v>411027</v>
       </c>
       <c r="R32" t="n">
-        <v>6709984</v>
+        <v>6710222</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3772,10 +3772,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132197647</v>
+        <v>132197615</v>
       </c>
       <c r="B33" t="n">
-        <v>79034</v>
+        <v>79895</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3783,21 +3783,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>410950</v>
+        <v>410939</v>
       </c>
       <c r="R33" t="n">
-        <v>6709984</v>
+        <v>6710183</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3869,10 +3869,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132197667</v>
+        <v>132197605</v>
       </c>
       <c r="B34" t="n">
-        <v>78942</v>
+        <v>79895</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3880,21 +3880,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>411027</v>
+        <v>410950</v>
       </c>
       <c r="R34" t="n">
-        <v>6710222</v>
+        <v>6709984</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132197655</v>
+        <v>132197653</v>
       </c>
       <c r="B35" t="n">
-        <v>79033</v>
+        <v>81261</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3977,21 +3977,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>411091</v>
+        <v>410972</v>
       </c>
       <c r="R35" t="n">
-        <v>6710283</v>
+        <v>6710194</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4045,7 +4045,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4064,10 +4063,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132197653</v>
+        <v>132197646</v>
       </c>
       <c r="B36" t="n">
-        <v>81261</v>
+        <v>79034</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,21 +4074,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4099,10 +4098,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>410972</v>
+        <v>410983</v>
       </c>
       <c r="R36" t="n">
-        <v>6710194</v>
+        <v>6709997</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4161,10 +4160,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132197646</v>
+        <v>132197659</v>
       </c>
       <c r="B37" t="n">
-        <v>79034</v>
+        <v>78942</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4172,21 +4171,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4196,10 +4195,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>410983</v>
+        <v>410973</v>
       </c>
       <c r="R37" t="n">
-        <v>6709997</v>
+        <v>6709994</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4240,6 +4239,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4258,10 +4258,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132197659</v>
+        <v>132197655</v>
       </c>
       <c r="B38" t="n">
-        <v>78942</v>
+        <v>79033</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,21 +4269,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>410973</v>
+        <v>411091</v>
       </c>
       <c r="R38" t="n">
-        <v>6709994</v>
+        <v>6710283</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4550,7 +4550,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132197634</v>
+        <v>132197632</v>
       </c>
       <c r="B41" t="n">
         <v>79895</v>
@@ -4585,10 +4585,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>410980</v>
+        <v>410998</v>
       </c>
       <c r="R41" t="n">
-        <v>6710008</v>
+        <v>6710163</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4647,7 +4647,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132197632</v>
+        <v>132197634</v>
       </c>
       <c r="B42" t="n">
         <v>79895</v>
@@ -4682,10 +4682,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>410998</v>
+        <v>410980</v>
       </c>
       <c r="R42" t="n">
-        <v>6710163</v>
+        <v>6710008</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4744,10 +4744,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132197600</v>
+        <v>132197609</v>
       </c>
       <c r="B43" t="n">
-        <v>78942</v>
+        <v>79895</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4755,21 +4755,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>410935</v>
+        <v>410902</v>
       </c>
       <c r="R43" t="n">
-        <v>6710081</v>
+        <v>6710163</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4841,10 +4841,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132197609</v>
+        <v>132197656</v>
       </c>
       <c r="B44" t="n">
-        <v>79895</v>
+        <v>79276</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4852,21 +4852,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4876,10 +4876,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>410902</v>
+        <v>410938</v>
       </c>
       <c r="R44" t="n">
-        <v>6710163</v>
+        <v>6710077</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4938,10 +4938,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132197656</v>
+        <v>132197600</v>
       </c>
       <c r="B45" t="n">
-        <v>79276</v>
+        <v>78942</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4949,21 +4949,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>410938</v>
+        <v>410935</v>
       </c>
       <c r="R45" t="n">
-        <v>6710077</v>
+        <v>6710081</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5132,7 +5132,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132197606</v>
+        <v>132197627</v>
       </c>
       <c r="B47" t="n">
         <v>79895</v>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>410946</v>
+        <v>410971</v>
       </c>
       <c r="R47" t="n">
-        <v>6709981</v>
+        <v>6710196</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5229,7 +5229,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132197627</v>
+        <v>132197606</v>
       </c>
       <c r="B48" t="n">
         <v>79895</v>
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>410971</v>
+        <v>410946</v>
       </c>
       <c r="R48" t="n">
-        <v>6710196</v>
+        <v>6709981</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5423,7 +5423,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132197628</v>
+        <v>132197629</v>
       </c>
       <c r="B50" t="n">
         <v>79895</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>410998</v>
+        <v>410993</v>
       </c>
       <c r="R50" t="n">
-        <v>6710174</v>
+        <v>6710175</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5520,7 +5520,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132197629</v>
+        <v>132197628</v>
       </c>
       <c r="B51" t="n">
         <v>79895</v>
@@ -5555,10 +5555,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>410993</v>
+        <v>410998</v>
       </c>
       <c r="R51" t="n">
-        <v>6710175</v>
+        <v>6710174</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5811,10 +5811,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132197660</v>
+        <v>132197616</v>
       </c>
       <c r="B54" t="n">
-        <v>78942</v>
+        <v>79895</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5822,21 +5822,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>410994</v>
+        <v>410952</v>
       </c>
       <c r="R54" t="n">
-        <v>6710185</v>
+        <v>6710170</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5890,7 +5890,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5909,10 +5908,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132197616</v>
+        <v>132197660</v>
       </c>
       <c r="B55" t="n">
-        <v>79895</v>
+        <v>78942</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5920,21 +5919,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5944,10 +5943,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>410952</v>
+        <v>410994</v>
       </c>
       <c r="R55" t="n">
-        <v>6710170</v>
+        <v>6710185</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5988,6 +5987,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6006,10 +6006,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132197664</v>
+        <v>132197607</v>
       </c>
       <c r="B56" t="n">
-        <v>78942</v>
+        <v>79895</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6017,21 +6017,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>410928</v>
+        <v>410933</v>
       </c>
       <c r="R56" t="n">
-        <v>6710090</v>
+        <v>6710072</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6103,10 +6103,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132197607</v>
+        <v>132197664</v>
       </c>
       <c r="B57" t="n">
-        <v>79895</v>
+        <v>78942</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6114,21 +6114,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6138,10 +6138,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>410933</v>
+        <v>410928</v>
       </c>
       <c r="R57" t="n">
-        <v>6710072</v>
+        <v>6710090</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>

--- a/artfynd/A 13525-2026 artfynd.xlsx
+++ b/artfynd/A 13525-2026 artfynd.xlsx
@@ -1347,32 +1347,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132197640</v>
+        <v>132197663</v>
       </c>
       <c r="B8" t="n">
-        <v>79362</v>
+        <v>78942</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6450</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410985</v>
+        <v>410929</v>
       </c>
       <c r="R8" t="n">
-        <v>6710205</v>
+        <v>6710058</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1444,32 +1444,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132197619</v>
+        <v>132197640</v>
       </c>
       <c r="B9" t="n">
-        <v>79895</v>
+        <v>79362</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6450</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>411038</v>
+        <v>410985</v>
       </c>
       <c r="R9" t="n">
-        <v>6710225</v>
+        <v>6710205</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132197648</v>
+        <v>132197619</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>79895</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>410933</v>
+        <v>411038</v>
       </c>
       <c r="R10" t="n">
-        <v>6710072</v>
+        <v>6710225</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132197663</v>
+        <v>132197648</v>
       </c>
       <c r="B12" t="n">
-        <v>78942</v>
+        <v>79034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410929</v>
+        <v>410933</v>
       </c>
       <c r="R12" t="n">
-        <v>6710058</v>
+        <v>6710072</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132197669</v>
+        <v>132197601</v>
       </c>
       <c r="B13" t="n">
-        <v>78942</v>
+        <v>79895</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,21 +1843,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>410992</v>
+        <v>410984</v>
       </c>
       <c r="R13" t="n">
-        <v>6710219</v>
+        <v>6709997</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132197666</v>
+        <v>132197669</v>
       </c>
       <c r="B14" t="n">
         <v>78942</v>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>410952</v>
+        <v>410992</v>
       </c>
       <c r="R14" t="n">
-        <v>6710169</v>
+        <v>6710219</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2026,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132197601</v>
+        <v>132197666</v>
       </c>
       <c r="B15" t="n">
-        <v>79895</v>
+        <v>78942</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>410984</v>
+        <v>410952</v>
       </c>
       <c r="R15" t="n">
-        <v>6709997</v>
+        <v>6710169</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2123,32 +2123,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132197643</v>
+        <v>132197665</v>
       </c>
       <c r="B16" t="n">
-        <v>79300</v>
+        <v>78942</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>410998</v>
+        <v>410902</v>
       </c>
       <c r="R16" t="n">
         <v>6710163</v>
@@ -2220,32 +2220,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132197635</v>
+        <v>132197643</v>
       </c>
       <c r="B17" t="n">
-        <v>79895</v>
+        <v>79300</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>410936</v>
+        <v>410998</v>
       </c>
       <c r="R17" t="n">
-        <v>6710017</v>
+        <v>6710163</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132197665</v>
+        <v>132197635</v>
       </c>
       <c r="B18" t="n">
-        <v>78942</v>
+        <v>79895</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>410902</v>
+        <v>410936</v>
       </c>
       <c r="R18" t="n">
-        <v>6710163</v>
+        <v>6710017</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2705,10 +2705,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132197652</v>
+        <v>132197631</v>
       </c>
       <c r="B22" t="n">
-        <v>79034</v>
+        <v>79895</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2716,21 +2716,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>410937</v>
+        <v>410991</v>
       </c>
       <c r="R22" t="n">
-        <v>6710017</v>
+        <v>6710191</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2802,7 +2802,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132197631</v>
+        <v>132197608</v>
       </c>
       <c r="B23" t="n">
         <v>79895</v>
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410991</v>
+        <v>410931</v>
       </c>
       <c r="R23" t="n">
-        <v>6710191</v>
+        <v>6710096</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132197608</v>
+        <v>132197652</v>
       </c>
       <c r="B24" t="n">
-        <v>79895</v>
+        <v>79034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2910,21 +2910,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410931</v>
+        <v>410937</v>
       </c>
       <c r="R24" t="n">
-        <v>6710096</v>
+        <v>6710017</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132197647</v>
+        <v>132197667</v>
       </c>
       <c r="B31" t="n">
-        <v>79034</v>
+        <v>78942</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>410950</v>
+        <v>411027</v>
       </c>
       <c r="R31" t="n">
-        <v>6709984</v>
+        <v>6710222</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132197667</v>
+        <v>132197605</v>
       </c>
       <c r="B32" t="n">
-        <v>78942</v>
+        <v>79895</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3686,21 +3686,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>411027</v>
+        <v>410950</v>
       </c>
       <c r="R32" t="n">
-        <v>6710222</v>
+        <v>6709984</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3869,10 +3869,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132197605</v>
+        <v>132197647</v>
       </c>
       <c r="B34" t="n">
-        <v>79895</v>
+        <v>79034</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3880,21 +3880,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4063,10 +4063,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132197646</v>
+        <v>132197659</v>
       </c>
       <c r="B36" t="n">
-        <v>79034</v>
+        <v>78942</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4074,21 +4074,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>410983</v>
+        <v>410973</v>
       </c>
       <c r="R36" t="n">
-        <v>6709997</v>
+        <v>6709994</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4142,6 +4142,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4160,10 +4161,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132197659</v>
+        <v>132197655</v>
       </c>
       <c r="B37" t="n">
-        <v>78942</v>
+        <v>79033</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4171,21 +4172,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4195,10 +4196,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>410973</v>
+        <v>411091</v>
       </c>
       <c r="R37" t="n">
-        <v>6709994</v>
+        <v>6710283</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4258,10 +4259,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132197655</v>
+        <v>132197646</v>
       </c>
       <c r="B38" t="n">
-        <v>79033</v>
+        <v>79034</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,21 +4270,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4293,10 +4294,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>411091</v>
+        <v>410983</v>
       </c>
       <c r="R38" t="n">
-        <v>6710283</v>
+        <v>6709997</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4337,7 +4338,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4744,10 +4744,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132197609</v>
+        <v>132197600</v>
       </c>
       <c r="B43" t="n">
-        <v>79895</v>
+        <v>78942</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4755,21 +4755,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>410902</v>
+        <v>410935</v>
       </c>
       <c r="R43" t="n">
-        <v>6710163</v>
+        <v>6710081</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4841,10 +4841,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132197656</v>
+        <v>132197609</v>
       </c>
       <c r="B44" t="n">
-        <v>79276</v>
+        <v>79895</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4852,21 +4852,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4876,10 +4876,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>410938</v>
+        <v>410902</v>
       </c>
       <c r="R44" t="n">
-        <v>6710077</v>
+        <v>6710163</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4938,10 +4938,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132197600</v>
+        <v>132197656</v>
       </c>
       <c r="B45" t="n">
-        <v>78942</v>
+        <v>79276</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4949,21 +4949,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>410935</v>
+        <v>410938</v>
       </c>
       <c r="R45" t="n">
-        <v>6710081</v>
+        <v>6710077</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5132,7 +5132,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132197627</v>
+        <v>132197606</v>
       </c>
       <c r="B47" t="n">
         <v>79895</v>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>410971</v>
+        <v>410946</v>
       </c>
       <c r="R47" t="n">
-        <v>6710196</v>
+        <v>6709981</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5229,10 +5229,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132197606</v>
+        <v>132197668</v>
       </c>
       <c r="B48" t="n">
-        <v>79895</v>
+        <v>78942</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5240,21 +5240,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>410946</v>
+        <v>411097</v>
       </c>
       <c r="R48" t="n">
-        <v>6709981</v>
+        <v>6710289</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5326,10 +5326,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132197668</v>
+        <v>132197627</v>
       </c>
       <c r="B49" t="n">
-        <v>78942</v>
+        <v>79895</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5337,21 +5337,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5361,10 +5361,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>411097</v>
+        <v>410971</v>
       </c>
       <c r="R49" t="n">
-        <v>6710289</v>
+        <v>6710196</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5811,10 +5811,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132197616</v>
+        <v>132197660</v>
       </c>
       <c r="B54" t="n">
-        <v>79895</v>
+        <v>78942</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5822,21 +5822,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>410952</v>
+        <v>410994</v>
       </c>
       <c r="R54" t="n">
-        <v>6710170</v>
+        <v>6710185</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5890,6 +5890,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5908,10 +5909,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132197660</v>
+        <v>132197616</v>
       </c>
       <c r="B55" t="n">
-        <v>78942</v>
+        <v>79895</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5919,21 +5920,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5943,10 +5944,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>410994</v>
+        <v>410952</v>
       </c>
       <c r="R55" t="n">
-        <v>6710185</v>
+        <v>6710170</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5987,7 +5988,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6006,10 +6006,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132197607</v>
+        <v>132197664</v>
       </c>
       <c r="B56" t="n">
-        <v>79895</v>
+        <v>78942</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6017,21 +6017,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>410933</v>
+        <v>410928</v>
       </c>
       <c r="R56" t="n">
-        <v>6710072</v>
+        <v>6710090</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6103,10 +6103,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132197664</v>
+        <v>132197607</v>
       </c>
       <c r="B57" t="n">
-        <v>78942</v>
+        <v>79895</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6114,21 +6114,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6138,10 +6138,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>410928</v>
+        <v>410933</v>
       </c>
       <c r="R57" t="n">
-        <v>6710090</v>
+        <v>6710072</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>

--- a/artfynd/A 13525-2026 artfynd.xlsx
+++ b/artfynd/A 13525-2026 artfynd.xlsx
@@ -2608,10 +2608,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132197633</v>
+        <v>132197652</v>
       </c>
       <c r="B21" t="n">
-        <v>79895</v>
+        <v>79034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,21 +2619,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>410961</v>
+        <v>410937</v>
       </c>
       <c r="R21" t="n">
-        <v>6710167</v>
+        <v>6710017</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2705,10 +2705,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132197631</v>
+        <v>132197651</v>
       </c>
       <c r="B22" t="n">
-        <v>79895</v>
+        <v>79034</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2716,21 +2716,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>410991</v>
+        <v>411000</v>
       </c>
       <c r="R22" t="n">
-        <v>6710191</v>
+        <v>6710007</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2802,7 +2802,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132197608</v>
+        <v>132197633</v>
       </c>
       <c r="B23" t="n">
         <v>79895</v>
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410931</v>
+        <v>410961</v>
       </c>
       <c r="R23" t="n">
-        <v>6710096</v>
+        <v>6710167</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132197652</v>
+        <v>132197631</v>
       </c>
       <c r="B24" t="n">
-        <v>79034</v>
+        <v>79895</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2910,21 +2910,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410937</v>
+        <v>410991</v>
       </c>
       <c r="R24" t="n">
-        <v>6710017</v>
+        <v>6710191</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2996,10 +2996,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132197651</v>
+        <v>132197608</v>
       </c>
       <c r="B25" t="n">
-        <v>79034</v>
+        <v>79895</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3007,21 +3007,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>411000</v>
+        <v>410931</v>
       </c>
       <c r="R25" t="n">
-        <v>6710007</v>
+        <v>6710096</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>

--- a/artfynd/A 13525-2026 artfynd.xlsx
+++ b/artfynd/A 13525-2026 artfynd.xlsx
@@ -1444,32 +1444,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132197640</v>
+        <v>132197630</v>
       </c>
       <c r="B9" t="n">
-        <v>79362</v>
+        <v>79895</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>410985</v>
+        <v>410994</v>
       </c>
       <c r="R9" t="n">
-        <v>6710205</v>
+        <v>6710184</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,32 +1541,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132197619</v>
+        <v>132197640</v>
       </c>
       <c r="B10" t="n">
-        <v>79895</v>
+        <v>79362</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6450</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>411038</v>
+        <v>410985</v>
       </c>
       <c r="R10" t="n">
-        <v>6710225</v>
+        <v>6710205</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132197630</v>
+        <v>132197619</v>
       </c>
       <c r="B11" t="n">
         <v>79895</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410994</v>
+        <v>411038</v>
       </c>
       <c r="R11" t="n">
-        <v>6710184</v>
+        <v>6710225</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132197601</v>
+        <v>132197669</v>
       </c>
       <c r="B13" t="n">
-        <v>79895</v>
+        <v>78942</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,21 +1843,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>410984</v>
+        <v>410992</v>
       </c>
       <c r="R13" t="n">
-        <v>6709997</v>
+        <v>6710219</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132197669</v>
+        <v>132197666</v>
       </c>
       <c r="B14" t="n">
         <v>78942</v>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>410992</v>
+        <v>410952</v>
       </c>
       <c r="R14" t="n">
-        <v>6710219</v>
+        <v>6710169</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2026,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132197666</v>
+        <v>132197601</v>
       </c>
       <c r="B15" t="n">
-        <v>78942</v>
+        <v>79895</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>410952</v>
+        <v>410984</v>
       </c>
       <c r="R15" t="n">
-        <v>6710169</v>
+        <v>6709997</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2608,10 +2608,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132197652</v>
+        <v>132197631</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>79895</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,21 +2619,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>410937</v>
+        <v>410991</v>
       </c>
       <c r="R21" t="n">
-        <v>6710017</v>
+        <v>6710191</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2705,10 +2705,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132197651</v>
+        <v>132197608</v>
       </c>
       <c r="B22" t="n">
-        <v>79034</v>
+        <v>79895</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2716,21 +2716,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>411000</v>
+        <v>410931</v>
       </c>
       <c r="R22" t="n">
-        <v>6710007</v>
+        <v>6710096</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132197631</v>
+        <v>132197652</v>
       </c>
       <c r="B24" t="n">
-        <v>79895</v>
+        <v>79034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2910,21 +2910,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410991</v>
+        <v>410937</v>
       </c>
       <c r="R24" t="n">
-        <v>6710191</v>
+        <v>6710017</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2996,10 +2996,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132197608</v>
+        <v>132197651</v>
       </c>
       <c r="B25" t="n">
-        <v>79895</v>
+        <v>79034</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3007,21 +3007,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410931</v>
+        <v>411000</v>
       </c>
       <c r="R25" t="n">
-        <v>6710096</v>
+        <v>6710007</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3093,10 +3093,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132197654</v>
+        <v>132197602</v>
       </c>
       <c r="B26" t="n">
-        <v>79033</v>
+        <v>79895</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3104,21 +3104,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410960</v>
+        <v>410973</v>
       </c>
       <c r="R26" t="n">
-        <v>6710167</v>
+        <v>6709995</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3190,10 +3190,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132197602</v>
+        <v>132197654</v>
       </c>
       <c r="B27" t="n">
-        <v>79895</v>
+        <v>79033</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3201,21 +3201,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>410973</v>
+        <v>410960</v>
       </c>
       <c r="R27" t="n">
-        <v>6709995</v>
+        <v>6710167</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132197667</v>
+        <v>132197615</v>
       </c>
       <c r="B31" t="n">
-        <v>78942</v>
+        <v>79895</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>411027</v>
+        <v>410939</v>
       </c>
       <c r="R31" t="n">
-        <v>6710222</v>
+        <v>6710183</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3772,10 +3772,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132197615</v>
+        <v>132197667</v>
       </c>
       <c r="B33" t="n">
-        <v>79895</v>
+        <v>78942</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3783,21 +3783,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>410939</v>
+        <v>411027</v>
       </c>
       <c r="R33" t="n">
-        <v>6710183</v>
+        <v>6710222</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132197653</v>
+        <v>132197646</v>
       </c>
       <c r="B35" t="n">
-        <v>81261</v>
+        <v>79034</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3977,21 +3977,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>410972</v>
+        <v>410983</v>
       </c>
       <c r="R35" t="n">
-        <v>6710194</v>
+        <v>6709997</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4063,10 +4063,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132197659</v>
+        <v>132197650</v>
       </c>
       <c r="B36" t="n">
-        <v>78942</v>
+        <v>79034</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4074,21 +4074,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>410973</v>
+        <v>410986</v>
       </c>
       <c r="R36" t="n">
-        <v>6709994</v>
+        <v>6710178</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4142,7 +4142,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4161,10 +4160,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132197655</v>
+        <v>132197653</v>
       </c>
       <c r="B37" t="n">
-        <v>79033</v>
+        <v>81261</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4172,21 +4171,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4196,10 +4195,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>411091</v>
+        <v>410972</v>
       </c>
       <c r="R37" t="n">
-        <v>6710283</v>
+        <v>6710194</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4240,7 +4239,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4259,10 +4257,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132197646</v>
+        <v>132197659</v>
       </c>
       <c r="B38" t="n">
-        <v>79034</v>
+        <v>78942</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4270,21 +4268,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4294,10 +4292,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>410983</v>
+        <v>410973</v>
       </c>
       <c r="R38" t="n">
-        <v>6709997</v>
+        <v>6709994</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4338,6 +4336,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4356,10 +4355,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132197650</v>
+        <v>132197655</v>
       </c>
       <c r="B39" t="n">
-        <v>79034</v>
+        <v>79033</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4367,21 +4366,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4391,10 +4390,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>410986</v>
+        <v>411091</v>
       </c>
       <c r="R39" t="n">
-        <v>6710178</v>
+        <v>6710283</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4435,6 +4434,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4550,7 +4550,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132197632</v>
+        <v>132197634</v>
       </c>
       <c r="B41" t="n">
         <v>79895</v>
@@ -4585,10 +4585,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>410998</v>
+        <v>410980</v>
       </c>
       <c r="R41" t="n">
-        <v>6710163</v>
+        <v>6710008</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4647,7 +4647,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132197634</v>
+        <v>132197632</v>
       </c>
       <c r="B42" t="n">
         <v>79895</v>
@@ -4682,10 +4682,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>410980</v>
+        <v>410998</v>
       </c>
       <c r="R42" t="n">
-        <v>6710008</v>
+        <v>6710163</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5132,10 +5132,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132197606</v>
+        <v>132197668</v>
       </c>
       <c r="B47" t="n">
-        <v>79895</v>
+        <v>78942</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5143,21 +5143,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>410946</v>
+        <v>411097</v>
       </c>
       <c r="R47" t="n">
-        <v>6709981</v>
+        <v>6710289</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5229,10 +5229,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132197668</v>
+        <v>132197627</v>
       </c>
       <c r="B48" t="n">
-        <v>78942</v>
+        <v>79895</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5240,21 +5240,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>411097</v>
+        <v>410971</v>
       </c>
       <c r="R48" t="n">
-        <v>6710289</v>
+        <v>6710196</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5326,7 +5326,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132197627</v>
+        <v>132197606</v>
       </c>
       <c r="B49" t="n">
         <v>79895</v>
@@ -5361,10 +5361,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>410971</v>
+        <v>410946</v>
       </c>
       <c r="R49" t="n">
-        <v>6710196</v>
+        <v>6709981</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5423,7 +5423,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132197629</v>
+        <v>132197628</v>
       </c>
       <c r="B50" t="n">
         <v>79895</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>410993</v>
+        <v>410998</v>
       </c>
       <c r="R50" t="n">
-        <v>6710175</v>
+        <v>6710174</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5520,7 +5520,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132197628</v>
+        <v>132197629</v>
       </c>
       <c r="B51" t="n">
         <v>79895</v>
@@ -5555,10 +5555,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>410998</v>
+        <v>410993</v>
       </c>
       <c r="R51" t="n">
-        <v>6710174</v>
+        <v>6710175</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>

--- a/artfynd/A 13525-2026 artfynd.xlsx
+++ b/artfynd/A 13525-2026 artfynd.xlsx
@@ -1347,32 +1347,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132197640</v>
+        <v>132197663</v>
       </c>
       <c r="B8" t="n">
-        <v>79401</v>
+        <v>78983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6450</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410985</v>
+        <v>410929</v>
       </c>
       <c r="R8" t="n">
-        <v>6710205</v>
+        <v>6710058</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132197619</v>
+        <v>132197630</v>
       </c>
       <c r="B9" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>411038</v>
+        <v>410994</v>
       </c>
       <c r="R9" t="n">
-        <v>6710225</v>
+        <v>6710184</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,32 +1541,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132197630</v>
+        <v>132197640</v>
       </c>
       <c r="B10" t="n">
-        <v>79934</v>
+        <v>79403</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6450</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>410994</v>
+        <v>410985</v>
       </c>
       <c r="R10" t="n">
-        <v>6710184</v>
+        <v>6710205</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132197663</v>
+        <v>132197619</v>
       </c>
       <c r="B11" t="n">
-        <v>78981</v>
+        <v>79936</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410929</v>
+        <v>411038</v>
       </c>
       <c r="R11" t="n">
-        <v>6710058</v>
+        <v>6710225</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1738,7 +1738,7 @@
         <v>132197648</v>
       </c>
       <c r="B12" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132197669</v>
+        <v>132197601</v>
       </c>
       <c r="B13" t="n">
-        <v>78981</v>
+        <v>79936</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,21 +1843,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>410992</v>
+        <v>410984</v>
       </c>
       <c r="R13" t="n">
-        <v>6710219</v>
+        <v>6709997</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132197666</v>
+        <v>132197669</v>
       </c>
       <c r="B14" t="n">
-        <v>78981</v>
+        <v>78983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>410952</v>
+        <v>410992</v>
       </c>
       <c r="R14" t="n">
-        <v>6710169</v>
+        <v>6710219</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2026,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132197601</v>
+        <v>132197666</v>
       </c>
       <c r="B15" t="n">
-        <v>79934</v>
+        <v>78983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>410984</v>
+        <v>410952</v>
       </c>
       <c r="R15" t="n">
-        <v>6709997</v>
+        <v>6710169</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2123,32 +2123,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132197665</v>
+        <v>132197643</v>
       </c>
       <c r="B16" t="n">
-        <v>78981</v>
+        <v>79341</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>410902</v>
+        <v>410998</v>
       </c>
       <c r="R16" t="n">
         <v>6710163</v>
@@ -2220,32 +2220,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132197643</v>
+        <v>132197635</v>
       </c>
       <c r="B17" t="n">
-        <v>79339</v>
+        <v>79936</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>410998</v>
+        <v>410936</v>
       </c>
       <c r="R17" t="n">
-        <v>6710163</v>
+        <v>6710017</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132197635</v>
+        <v>132197665</v>
       </c>
       <c r="B18" t="n">
-        <v>79934</v>
+        <v>78983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>410936</v>
+        <v>410902</v>
       </c>
       <c r="R18" t="n">
-        <v>6710017</v>
+        <v>6710163</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2417,7 +2417,7 @@
         <v>132197670</v>
       </c>
       <c r="B19" t="n">
-        <v>78981</v>
+        <v>78983</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>132197671</v>
       </c>
       <c r="B20" t="n">
-        <v>78981</v>
+        <v>78983</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>132197633</v>
       </c>
       <c r="B21" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>132197631</v>
       </c>
       <c r="B22" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>132197608</v>
       </c>
       <c r="B23" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>132197651</v>
       </c>
       <c r="B24" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>132197652</v>
       </c>
       <c r="B25" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>132197654</v>
       </c>
       <c r="B26" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>132197602</v>
       </c>
       <c r="B27" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>132197644</v>
       </c>
       <c r="B28" t="n">
-        <v>79339</v>
+        <v>79341</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>132197636</v>
       </c>
       <c r="B29" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>132197637</v>
       </c>
       <c r="B30" t="n">
-        <v>79905</v>
+        <v>79907</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132197667</v>
+        <v>132197605</v>
       </c>
       <c r="B31" t="n">
-        <v>78981</v>
+        <v>79936</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>411027</v>
+        <v>410950</v>
       </c>
       <c r="R31" t="n">
-        <v>6710222</v>
+        <v>6709984</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132197605</v>
+        <v>132197615</v>
       </c>
       <c r="B32" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>410950</v>
+        <v>410939</v>
       </c>
       <c r="R32" t="n">
-        <v>6709984</v>
+        <v>6710183</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3772,10 +3772,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132197615</v>
+        <v>132197667</v>
       </c>
       <c r="B33" t="n">
-        <v>79934</v>
+        <v>78983</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3783,21 +3783,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>410939</v>
+        <v>411027</v>
       </c>
       <c r="R33" t="n">
-        <v>6710183</v>
+        <v>6710222</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3872,7 +3872,7 @@
         <v>132197647</v>
       </c>
       <c r="B34" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132197655</v>
+        <v>132197650</v>
       </c>
       <c r="B35" t="n">
-        <v>79072</v>
+        <v>79075</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3977,21 +3977,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>411091</v>
+        <v>410986</v>
       </c>
       <c r="R35" t="n">
-        <v>6710283</v>
+        <v>6710178</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4045,7 +4045,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4064,10 +4063,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132197650</v>
+        <v>132197646</v>
       </c>
       <c r="B36" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4099,10 +4098,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>410986</v>
+        <v>410983</v>
       </c>
       <c r="R36" t="n">
-        <v>6710178</v>
+        <v>6709997</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4161,10 +4160,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132197646</v>
+        <v>132197655</v>
       </c>
       <c r="B37" t="n">
-        <v>79073</v>
+        <v>79074</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4172,21 +4171,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4196,10 +4195,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>410983</v>
+        <v>411091</v>
       </c>
       <c r="R37" t="n">
-        <v>6709997</v>
+        <v>6710283</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4240,6 +4239,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4261,7 +4261,7 @@
         <v>132197653</v>
       </c>
       <c r="B38" t="n">
-        <v>81300</v>
+        <v>81302</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>132197659</v>
       </c>
       <c r="B39" t="n">
-        <v>78981</v>
+        <v>78983</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>132197618</v>
       </c>
       <c r="B40" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>132197632</v>
       </c>
       <c r="B41" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>132197634</v>
       </c>
       <c r="B42" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>132197600</v>
       </c>
       <c r="B43" t="n">
-        <v>78981</v>
+        <v>78983</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4841,10 +4841,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132197609</v>
+        <v>132197656</v>
       </c>
       <c r="B44" t="n">
-        <v>79934</v>
+        <v>79317</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4852,21 +4852,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4876,10 +4876,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>410902</v>
+        <v>410938</v>
       </c>
       <c r="R44" t="n">
-        <v>6710163</v>
+        <v>6710077</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4938,10 +4938,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132197656</v>
+        <v>132197609</v>
       </c>
       <c r="B45" t="n">
-        <v>79315</v>
+        <v>79936</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4949,21 +4949,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>410938</v>
+        <v>410902</v>
       </c>
       <c r="R45" t="n">
-        <v>6710077</v>
+        <v>6710163</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5038,7 +5038,7 @@
         <v>132197662</v>
       </c>
       <c r="B46" t="n">
-        <v>78981</v>
+        <v>78983</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>132197627</v>
       </c>
       <c r="B47" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>132197606</v>
       </c>
       <c r="B48" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>132197668</v>
       </c>
       <c r="B49" t="n">
-        <v>78981</v>
+        <v>78983</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>132197629</v>
       </c>
       <c r="B50" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>132197628</v>
       </c>
       <c r="B51" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         <v>132197604</v>
       </c>
       <c r="B52" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>132197661</v>
       </c>
       <c r="B53" t="n">
-        <v>78981</v>
+        <v>78983</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5811,10 +5811,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132197660</v>
+        <v>132197616</v>
       </c>
       <c r="B54" t="n">
-        <v>78981</v>
+        <v>79936</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5822,21 +5822,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>410994</v>
+        <v>410952</v>
       </c>
       <c r="R54" t="n">
-        <v>6710185</v>
+        <v>6710170</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5890,7 +5890,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5909,10 +5908,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132197616</v>
+        <v>132197660</v>
       </c>
       <c r="B55" t="n">
-        <v>79934</v>
+        <v>78983</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5920,21 +5919,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5944,10 +5943,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>410952</v>
+        <v>410994</v>
       </c>
       <c r="R55" t="n">
-        <v>6710170</v>
+        <v>6710185</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5988,6 +5987,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6009,7 +6009,7 @@
         <v>132197607</v>
       </c>
       <c r="B56" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>132197664</v>
       </c>
       <c r="B57" t="n">
-        <v>78981</v>
+        <v>78983</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 13525-2026 artfynd.xlsx
+++ b/artfynd/A 13525-2026 artfynd.xlsx
@@ -2608,7 +2608,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132197633</v>
+        <v>132197631</v>
       </c>
       <c r="B21" t="n">
         <v>79936</v>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>410961</v>
+        <v>410991</v>
       </c>
       <c r="R21" t="n">
-        <v>6710167</v>
+        <v>6710191</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2705,7 +2705,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132197631</v>
+        <v>132197608</v>
       </c>
       <c r="B22" t="n">
         <v>79936</v>
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>410991</v>
+        <v>410931</v>
       </c>
       <c r="R22" t="n">
-        <v>6710191</v>
+        <v>6710096</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2802,7 +2802,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132197608</v>
+        <v>132197633</v>
       </c>
       <c r="B23" t="n">
         <v>79936</v>
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410931</v>
+        <v>410961</v>
       </c>
       <c r="R23" t="n">
-        <v>6710096</v>
+        <v>6710167</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132197605</v>
+        <v>132197647</v>
       </c>
       <c r="B31" t="n">
-        <v>79936</v>
+        <v>79075</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132197615</v>
+        <v>132197667</v>
       </c>
       <c r="B32" t="n">
-        <v>79936</v>
+        <v>78983</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3686,21 +3686,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>410939</v>
+        <v>411027</v>
       </c>
       <c r="R32" t="n">
-        <v>6710183</v>
+        <v>6710222</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3772,10 +3772,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132197667</v>
+        <v>132197605</v>
       </c>
       <c r="B33" t="n">
-        <v>78983</v>
+        <v>79936</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3783,21 +3783,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>411027</v>
+        <v>410950</v>
       </c>
       <c r="R33" t="n">
-        <v>6710222</v>
+        <v>6709984</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3869,10 +3869,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132197647</v>
+        <v>132197615</v>
       </c>
       <c r="B34" t="n">
-        <v>79075</v>
+        <v>79936</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3880,21 +3880,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>410950</v>
+        <v>410939</v>
       </c>
       <c r="R34" t="n">
-        <v>6709984</v>
+        <v>6710183</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>

--- a/artfynd/A 13525-2026 artfynd.xlsx
+++ b/artfynd/A 13525-2026 artfynd.xlsx
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132197663</v>
+        <v>132197648</v>
       </c>
       <c r="B8" t="n">
-        <v>78983</v>
+        <v>79075</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,21 +1358,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410929</v>
+        <v>410933</v>
       </c>
       <c r="R8" t="n">
-        <v>6710058</v>
+        <v>6710072</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1444,32 +1444,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132197630</v>
+        <v>132197640</v>
       </c>
       <c r="B9" t="n">
-        <v>79936</v>
+        <v>79403</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6450</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>410994</v>
+        <v>410985</v>
       </c>
       <c r="R9" t="n">
-        <v>6710184</v>
+        <v>6710205</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,32 +1541,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132197640</v>
+        <v>132197619</v>
       </c>
       <c r="B10" t="n">
-        <v>79403</v>
+        <v>79936</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>410985</v>
+        <v>411038</v>
       </c>
       <c r="R10" t="n">
-        <v>6710205</v>
+        <v>6710225</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132197619</v>
+        <v>132197630</v>
       </c>
       <c r="B11" t="n">
         <v>79936</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>411038</v>
+        <v>410994</v>
       </c>
       <c r="R11" t="n">
-        <v>6710225</v>
+        <v>6710184</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132197648</v>
+        <v>132197663</v>
       </c>
       <c r="B12" t="n">
-        <v>79075</v>
+        <v>78983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410933</v>
+        <v>410929</v>
       </c>
       <c r="R12" t="n">
-        <v>6710072</v>
+        <v>6710058</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>

--- a/artfynd/A 13525-2026 artfynd.xlsx
+++ b/artfynd/A 13525-2026 artfynd.xlsx
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132197601</v>
+        <v>132197669</v>
       </c>
       <c r="B13" t="n">
-        <v>79936</v>
+        <v>78983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,21 +1843,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>410984</v>
+        <v>410992</v>
       </c>
       <c r="R13" t="n">
-        <v>6709997</v>
+        <v>6710219</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132197669</v>
+        <v>132197666</v>
       </c>
       <c r="B14" t="n">
         <v>78983</v>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>410992</v>
+        <v>410952</v>
       </c>
       <c r="R14" t="n">
-        <v>6710219</v>
+        <v>6710169</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2026,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132197666</v>
+        <v>132197601</v>
       </c>
       <c r="B15" t="n">
-        <v>78983</v>
+        <v>79936</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>410952</v>
+        <v>410984</v>
       </c>
       <c r="R15" t="n">
-        <v>6710169</v>
+        <v>6709997</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2608,7 +2608,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132197631</v>
+        <v>132197633</v>
       </c>
       <c r="B21" t="n">
         <v>79936</v>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>410991</v>
+        <v>410961</v>
       </c>
       <c r="R21" t="n">
-        <v>6710191</v>
+        <v>6710167</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2705,7 +2705,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132197608</v>
+        <v>132197631</v>
       </c>
       <c r="B22" t="n">
         <v>79936</v>
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>410931</v>
+        <v>410991</v>
       </c>
       <c r="R22" t="n">
-        <v>6710096</v>
+        <v>6710191</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2802,7 +2802,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132197633</v>
+        <v>132197608</v>
       </c>
       <c r="B23" t="n">
         <v>79936</v>
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410961</v>
+        <v>410931</v>
       </c>
       <c r="R23" t="n">
-        <v>6710167</v>
+        <v>6710096</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2899,7 +2899,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132197651</v>
+        <v>132197652</v>
       </c>
       <c r="B24" t="n">
         <v>79075</v>
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>411000</v>
+        <v>410937</v>
       </c>
       <c r="R24" t="n">
-        <v>6710007</v>
+        <v>6710017</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2996,7 +2996,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132197652</v>
+        <v>132197651</v>
       </c>
       <c r="B25" t="n">
         <v>79075</v>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410937</v>
+        <v>411000</v>
       </c>
       <c r="R25" t="n">
-        <v>6710017</v>
+        <v>6710007</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3093,10 +3093,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132197654</v>
+        <v>132197602</v>
       </c>
       <c r="B26" t="n">
-        <v>79074</v>
+        <v>79936</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3104,21 +3104,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410960</v>
+        <v>410973</v>
       </c>
       <c r="R26" t="n">
-        <v>6710167</v>
+        <v>6709995</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3190,10 +3190,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132197602</v>
+        <v>132197654</v>
       </c>
       <c r="B27" t="n">
-        <v>79936</v>
+        <v>79074</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3201,21 +3201,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>410973</v>
+        <v>410960</v>
       </c>
       <c r="R27" t="n">
-        <v>6709995</v>
+        <v>6710167</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132197647</v>
+        <v>132197605</v>
       </c>
       <c r="B31" t="n">
-        <v>79075</v>
+        <v>79936</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132197667</v>
+        <v>132197615</v>
       </c>
       <c r="B32" t="n">
-        <v>78983</v>
+        <v>79936</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3686,21 +3686,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>411027</v>
+        <v>410939</v>
       </c>
       <c r="R32" t="n">
-        <v>6710222</v>
+        <v>6710183</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3772,10 +3772,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132197605</v>
+        <v>132197667</v>
       </c>
       <c r="B33" t="n">
-        <v>79936</v>
+        <v>78983</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3783,21 +3783,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>410950</v>
+        <v>411027</v>
       </c>
       <c r="R33" t="n">
-        <v>6709984</v>
+        <v>6710222</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3869,10 +3869,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132197615</v>
+        <v>132197647</v>
       </c>
       <c r="B34" t="n">
-        <v>79936</v>
+        <v>79075</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3880,21 +3880,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>410939</v>
+        <v>410950</v>
       </c>
       <c r="R34" t="n">
-        <v>6710183</v>
+        <v>6709984</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132197650</v>
+        <v>132197646</v>
       </c>
       <c r="B35" t="n">
         <v>79075</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>410986</v>
+        <v>410983</v>
       </c>
       <c r="R35" t="n">
-        <v>6710178</v>
+        <v>6709997</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4063,7 +4063,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132197646</v>
+        <v>132197650</v>
       </c>
       <c r="B36" t="n">
         <v>79075</v>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>410983</v>
+        <v>410986</v>
       </c>
       <c r="R36" t="n">
-        <v>6709997</v>
+        <v>6710178</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4841,10 +4841,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132197656</v>
+        <v>132197609</v>
       </c>
       <c r="B44" t="n">
-        <v>79317</v>
+        <v>79936</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4852,21 +4852,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4876,10 +4876,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>410938</v>
+        <v>410902</v>
       </c>
       <c r="R44" t="n">
-        <v>6710077</v>
+        <v>6710163</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4938,10 +4938,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132197609</v>
+        <v>132197656</v>
       </c>
       <c r="B45" t="n">
-        <v>79936</v>
+        <v>79317</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4949,21 +4949,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>410902</v>
+        <v>410938</v>
       </c>
       <c r="R45" t="n">
-        <v>6710163</v>
+        <v>6710077</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5132,10 +5132,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132197627</v>
+        <v>132197668</v>
       </c>
       <c r="B47" t="n">
-        <v>79936</v>
+        <v>78983</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5143,21 +5143,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>410971</v>
+        <v>411097</v>
       </c>
       <c r="R47" t="n">
-        <v>6710196</v>
+        <v>6710289</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5229,7 +5229,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132197606</v>
+        <v>132197627</v>
       </c>
       <c r="B48" t="n">
         <v>79936</v>
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>410946</v>
+        <v>410971</v>
       </c>
       <c r="R48" t="n">
-        <v>6709981</v>
+        <v>6710196</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5326,10 +5326,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132197668</v>
+        <v>132197606</v>
       </c>
       <c r="B49" t="n">
-        <v>78983</v>
+        <v>79936</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5337,21 +5337,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5361,10 +5361,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>411097</v>
+        <v>410946</v>
       </c>
       <c r="R49" t="n">
-        <v>6710289</v>
+        <v>6709981</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>

--- a/artfynd/A 13525-2026 artfynd.xlsx
+++ b/artfynd/A 13525-2026 artfynd.xlsx
@@ -2123,32 +2123,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132197643</v>
+        <v>132197665</v>
       </c>
       <c r="B16" t="n">
-        <v>79341</v>
+        <v>78983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>410998</v>
+        <v>410902</v>
       </c>
       <c r="R16" t="n">
         <v>6710163</v>
@@ -2220,32 +2220,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132197635</v>
+        <v>132197643</v>
       </c>
       <c r="B17" t="n">
-        <v>79936</v>
+        <v>79341</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>410936</v>
+        <v>410998</v>
       </c>
       <c r="R17" t="n">
-        <v>6710017</v>
+        <v>6710163</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132197665</v>
+        <v>132197635</v>
       </c>
       <c r="B18" t="n">
-        <v>78983</v>
+        <v>79936</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>410902</v>
+        <v>410936</v>
       </c>
       <c r="R18" t="n">
-        <v>6710163</v>
+        <v>6710017</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -4744,10 +4744,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132197600</v>
+        <v>132197609</v>
       </c>
       <c r="B43" t="n">
-        <v>78983</v>
+        <v>79936</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4755,21 +4755,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>410935</v>
+        <v>410902</v>
       </c>
       <c r="R43" t="n">
-        <v>6710081</v>
+        <v>6710163</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4841,10 +4841,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132197609</v>
+        <v>132197656</v>
       </c>
       <c r="B44" t="n">
-        <v>79936</v>
+        <v>79317</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4852,21 +4852,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4876,10 +4876,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>410902</v>
+        <v>410938</v>
       </c>
       <c r="R44" t="n">
-        <v>6710163</v>
+        <v>6710077</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4938,10 +4938,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132197656</v>
+        <v>132197600</v>
       </c>
       <c r="B45" t="n">
-        <v>79317</v>
+        <v>78983</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4949,21 +4949,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>410938</v>
+        <v>410935</v>
       </c>
       <c r="R45" t="n">
-        <v>6710077</v>
+        <v>6710081</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>

--- a/artfynd/A 13525-2026 artfynd.xlsx
+++ b/artfynd/A 13525-2026 artfynd.xlsx
@@ -2123,32 +2123,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132197665</v>
+        <v>132197643</v>
       </c>
       <c r="B16" t="n">
-        <v>78983</v>
+        <v>79341</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>410902</v>
+        <v>410998</v>
       </c>
       <c r="R16" t="n">
         <v>6710163</v>
@@ -2220,32 +2220,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132197643</v>
+        <v>132197635</v>
       </c>
       <c r="B17" t="n">
-        <v>79341</v>
+        <v>79936</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>410998</v>
+        <v>410936</v>
       </c>
       <c r="R17" t="n">
-        <v>6710163</v>
+        <v>6710017</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132197635</v>
+        <v>132197665</v>
       </c>
       <c r="B18" t="n">
-        <v>79936</v>
+        <v>78983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>410936</v>
+        <v>410902</v>
       </c>
       <c r="R18" t="n">
-        <v>6710017</v>
+        <v>6710163</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132197605</v>
+        <v>132197647</v>
       </c>
       <c r="B31" t="n">
-        <v>79936</v>
+        <v>79075</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3675,7 +3675,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132197615</v>
+        <v>132197605</v>
       </c>
       <c r="B32" t="n">
         <v>79936</v>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>410939</v>
+        <v>410950</v>
       </c>
       <c r="R32" t="n">
-        <v>6710183</v>
+        <v>6709984</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3772,10 +3772,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132197667</v>
+        <v>132197615</v>
       </c>
       <c r="B33" t="n">
-        <v>78983</v>
+        <v>79936</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3783,21 +3783,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>411027</v>
+        <v>410939</v>
       </c>
       <c r="R33" t="n">
-        <v>6710222</v>
+        <v>6710183</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3869,10 +3869,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132197647</v>
+        <v>132197667</v>
       </c>
       <c r="B34" t="n">
-        <v>79075</v>
+        <v>78983</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3880,21 +3880,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>410950</v>
+        <v>411027</v>
       </c>
       <c r="R34" t="n">
-        <v>6709984</v>
+        <v>6710222</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4744,10 +4744,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132197609</v>
+        <v>132197600</v>
       </c>
       <c r="B43" t="n">
-        <v>79936</v>
+        <v>78983</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4755,21 +4755,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>410902</v>
+        <v>410935</v>
       </c>
       <c r="R43" t="n">
-        <v>6710163</v>
+        <v>6710081</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4841,10 +4841,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132197656</v>
+        <v>132197609</v>
       </c>
       <c r="B44" t="n">
-        <v>79317</v>
+        <v>79936</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4852,21 +4852,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4876,10 +4876,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>410938</v>
+        <v>410902</v>
       </c>
       <c r="R44" t="n">
-        <v>6710077</v>
+        <v>6710163</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4938,10 +4938,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132197600</v>
+        <v>132197656</v>
       </c>
       <c r="B45" t="n">
-        <v>78983</v>
+        <v>79317</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4949,21 +4949,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>410935</v>
+        <v>410938</v>
       </c>
       <c r="R45" t="n">
-        <v>6710081</v>
+        <v>6710077</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>

--- a/artfynd/A 13525-2026 artfynd.xlsx
+++ b/artfynd/A 13525-2026 artfynd.xlsx
@@ -3093,10 +3093,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132197602</v>
+        <v>132197654</v>
       </c>
       <c r="B26" t="n">
-        <v>79936</v>
+        <v>79074</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3104,21 +3104,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410973</v>
+        <v>410960</v>
       </c>
       <c r="R26" t="n">
-        <v>6709995</v>
+        <v>6710167</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3190,10 +3190,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132197654</v>
+        <v>132197602</v>
       </c>
       <c r="B27" t="n">
-        <v>79074</v>
+        <v>79936</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3201,21 +3201,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>410960</v>
+        <v>410973</v>
       </c>
       <c r="R27" t="n">
-        <v>6710167</v>
+        <v>6709995</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132197646</v>
+        <v>132197659</v>
       </c>
       <c r="B35" t="n">
-        <v>79075</v>
+        <v>78983</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3977,21 +3977,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>410983</v>
+        <v>410973</v>
       </c>
       <c r="R35" t="n">
-        <v>6709997</v>
+        <v>6709994</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4045,6 +4045,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4063,7 +4064,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132197650</v>
+        <v>132197646</v>
       </c>
       <c r="B36" t="n">
         <v>79075</v>
@@ -4098,10 +4099,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>410986</v>
+        <v>410983</v>
       </c>
       <c r="R36" t="n">
-        <v>6710178</v>
+        <v>6709997</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4160,10 +4161,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132197655</v>
+        <v>132197650</v>
       </c>
       <c r="B37" t="n">
-        <v>79074</v>
+        <v>79075</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4171,21 +4172,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4195,10 +4196,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>411091</v>
+        <v>410986</v>
       </c>
       <c r="R37" t="n">
-        <v>6710283</v>
+        <v>6710178</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4239,7 +4240,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4258,10 +4258,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132197653</v>
+        <v>132197655</v>
       </c>
       <c r="B38" t="n">
-        <v>81302</v>
+        <v>79074</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,21 +4269,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>410972</v>
+        <v>411091</v>
       </c>
       <c r="R38" t="n">
-        <v>6710194</v>
+        <v>6710283</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4337,6 +4337,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4355,10 +4356,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132197659</v>
+        <v>132197653</v>
       </c>
       <c r="B39" t="n">
-        <v>78983</v>
+        <v>81302</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4366,21 +4367,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4390,10 +4391,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>410973</v>
+        <v>410972</v>
       </c>
       <c r="R39" t="n">
-        <v>6709994</v>
+        <v>6710194</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4434,7 +4435,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4744,10 +4744,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132197600</v>
+        <v>132197609</v>
       </c>
       <c r="B43" t="n">
-        <v>78983</v>
+        <v>79936</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4755,21 +4755,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>410935</v>
+        <v>410902</v>
       </c>
       <c r="R43" t="n">
-        <v>6710081</v>
+        <v>6710163</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4841,10 +4841,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132197609</v>
+        <v>132197656</v>
       </c>
       <c r="B44" t="n">
-        <v>79936</v>
+        <v>79317</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4852,21 +4852,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4876,10 +4876,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>410902</v>
+        <v>410938</v>
       </c>
       <c r="R44" t="n">
-        <v>6710163</v>
+        <v>6710077</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4938,10 +4938,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132197656</v>
+        <v>132197600</v>
       </c>
       <c r="B45" t="n">
-        <v>79317</v>
+        <v>78983</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4949,21 +4949,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>410938</v>
+        <v>410935</v>
       </c>
       <c r="R45" t="n">
-        <v>6710077</v>
+        <v>6710081</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>

--- a/artfynd/A 13525-2026 artfynd.xlsx
+++ b/artfynd/A 13525-2026 artfynd.xlsx
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132197648</v>
+        <v>132197630</v>
       </c>
       <c r="B8" t="n">
-        <v>79075</v>
+        <v>79938</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,21 +1358,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410933</v>
+        <v>410994</v>
       </c>
       <c r="R8" t="n">
-        <v>6710072</v>
+        <v>6710184</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1444,32 +1444,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132197640</v>
+        <v>132197619</v>
       </c>
       <c r="B9" t="n">
-        <v>79403</v>
+        <v>79938</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>410985</v>
+        <v>411038</v>
       </c>
       <c r="R9" t="n">
-        <v>6710205</v>
+        <v>6710225</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132197619</v>
+        <v>132197663</v>
       </c>
       <c r="B10" t="n">
-        <v>79936</v>
+        <v>78985</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>411038</v>
+        <v>410929</v>
       </c>
       <c r="R10" t="n">
-        <v>6710225</v>
+        <v>6710058</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1638,32 +1638,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132197630</v>
+        <v>132197640</v>
       </c>
       <c r="B11" t="n">
-        <v>79936</v>
+        <v>79405</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6450</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410994</v>
+        <v>410985</v>
       </c>
       <c r="R11" t="n">
-        <v>6710184</v>
+        <v>6710205</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132197663</v>
+        <v>132197648</v>
       </c>
       <c r="B12" t="n">
-        <v>78983</v>
+        <v>79077</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410929</v>
+        <v>410933</v>
       </c>
       <c r="R12" t="n">
-        <v>6710058</v>
+        <v>6710072</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1835,7 +1835,7 @@
         <v>132197669</v>
       </c>
       <c r="B13" t="n">
-        <v>78983</v>
+        <v>78985</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>132197666</v>
       </c>
       <c r="B14" t="n">
-        <v>78983</v>
+        <v>78985</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>132197601</v>
       </c>
       <c r="B15" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>132197643</v>
       </c>
       <c r="B16" t="n">
-        <v>79341</v>
+        <v>79343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>132197635</v>
       </c>
       <c r="B17" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>132197665</v>
       </c>
       <c r="B18" t="n">
-        <v>78983</v>
+        <v>78985</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132197670</v>
+        <v>132197671</v>
       </c>
       <c r="B19" t="n">
-        <v>78983</v>
+        <v>78985</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>410995</v>
+        <v>410977</v>
       </c>
       <c r="R19" t="n">
-        <v>6710181</v>
+        <v>6710177</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132197671</v>
+        <v>132197670</v>
       </c>
       <c r="B20" t="n">
-        <v>78983</v>
+        <v>78985</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>410977</v>
+        <v>410995</v>
       </c>
       <c r="R20" t="n">
-        <v>6710177</v>
+        <v>6710181</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2608,10 +2608,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132197633</v>
+        <v>132197631</v>
       </c>
       <c r="B21" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>410961</v>
+        <v>410991</v>
       </c>
       <c r="R21" t="n">
-        <v>6710167</v>
+        <v>6710191</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2705,10 +2705,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132197631</v>
+        <v>132197608</v>
       </c>
       <c r="B22" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>410991</v>
+        <v>410931</v>
       </c>
       <c r="R22" t="n">
-        <v>6710191</v>
+        <v>6710096</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2802,10 +2802,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132197608</v>
+        <v>132197633</v>
       </c>
       <c r="B23" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410931</v>
+        <v>410961</v>
       </c>
       <c r="R23" t="n">
-        <v>6710096</v>
+        <v>6710167</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2902,7 +2902,7 @@
         <v>132197652</v>
       </c>
       <c r="B24" t="n">
-        <v>79075</v>
+        <v>79077</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>132197651</v>
       </c>
       <c r="B25" t="n">
-        <v>79075</v>
+        <v>79077</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3093,10 +3093,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132197654</v>
+        <v>132197602</v>
       </c>
       <c r="B26" t="n">
-        <v>79074</v>
+        <v>79938</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3104,21 +3104,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410960</v>
+        <v>410973</v>
       </c>
       <c r="R26" t="n">
-        <v>6710167</v>
+        <v>6709995</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3190,10 +3190,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132197602</v>
+        <v>132197654</v>
       </c>
       <c r="B27" t="n">
-        <v>79936</v>
+        <v>79076</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3201,21 +3201,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>410973</v>
+        <v>410960</v>
       </c>
       <c r="R27" t="n">
-        <v>6709995</v>
+        <v>6710167</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3290,7 +3290,7 @@
         <v>132197644</v>
       </c>
       <c r="B28" t="n">
-        <v>79341</v>
+        <v>79343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>132197636</v>
       </c>
       <c r="B29" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>132197637</v>
       </c>
       <c r="B30" t="n">
-        <v>79907</v>
+        <v>79909</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132197647</v>
+        <v>132197667</v>
       </c>
       <c r="B31" t="n">
-        <v>79075</v>
+        <v>78985</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>410950</v>
+        <v>411027</v>
       </c>
       <c r="R31" t="n">
-        <v>6709984</v>
+        <v>6710222</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132197605</v>
+        <v>132197615</v>
       </c>
       <c r="B32" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>410950</v>
+        <v>410939</v>
       </c>
       <c r="R32" t="n">
-        <v>6709984</v>
+        <v>6710183</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3772,10 +3772,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132197615</v>
+        <v>132197605</v>
       </c>
       <c r="B33" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>410939</v>
+        <v>410950</v>
       </c>
       <c r="R33" t="n">
-        <v>6710183</v>
+        <v>6709984</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3869,10 +3869,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132197667</v>
+        <v>132197647</v>
       </c>
       <c r="B34" t="n">
-        <v>78983</v>
+        <v>79077</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3880,21 +3880,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>411027</v>
+        <v>410950</v>
       </c>
       <c r="R34" t="n">
-        <v>6710222</v>
+        <v>6709984</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132197659</v>
+        <v>132197653</v>
       </c>
       <c r="B35" t="n">
-        <v>78983</v>
+        <v>81304</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3977,21 +3977,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>410973</v>
+        <v>410972</v>
       </c>
       <c r="R35" t="n">
-        <v>6709994</v>
+        <v>6710194</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4045,7 +4045,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4064,10 +4063,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132197646</v>
+        <v>132197659</v>
       </c>
       <c r="B36" t="n">
-        <v>79075</v>
+        <v>78985</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,21 +4074,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4099,10 +4098,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>410983</v>
+        <v>410973</v>
       </c>
       <c r="R36" t="n">
-        <v>6709997</v>
+        <v>6709994</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4143,6 +4142,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132197650</v>
+        <v>132197646</v>
       </c>
       <c r="B37" t="n">
-        <v>79075</v>
+        <v>79077</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>410986</v>
+        <v>410983</v>
       </c>
       <c r="R37" t="n">
-        <v>6710178</v>
+        <v>6709997</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4258,10 +4258,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132197655</v>
+        <v>132197650</v>
       </c>
       <c r="B38" t="n">
-        <v>79074</v>
+        <v>79077</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,21 +4269,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>411091</v>
+        <v>410986</v>
       </c>
       <c r="R38" t="n">
-        <v>6710283</v>
+        <v>6710178</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4337,7 +4337,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4356,10 +4355,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132197653</v>
+        <v>132197655</v>
       </c>
       <c r="B39" t="n">
-        <v>81302</v>
+        <v>79076</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4367,21 +4366,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4391,10 +4390,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>410972</v>
+        <v>411091</v>
       </c>
       <c r="R39" t="n">
-        <v>6710194</v>
+        <v>6710283</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4435,6 +4434,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4456,7 +4456,7 @@
         <v>132197618</v>
       </c>
       <c r="B40" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4550,10 +4550,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132197632</v>
+        <v>132197634</v>
       </c>
       <c r="B41" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4585,10 +4585,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>410998</v>
+        <v>410980</v>
       </c>
       <c r="R41" t="n">
-        <v>6710163</v>
+        <v>6710008</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4647,10 +4647,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132197634</v>
+        <v>132197632</v>
       </c>
       <c r="B42" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4682,10 +4682,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>410980</v>
+        <v>410998</v>
       </c>
       <c r="R42" t="n">
-        <v>6710008</v>
+        <v>6710163</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4744,10 +4744,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132197609</v>
+        <v>132197600</v>
       </c>
       <c r="B43" t="n">
-        <v>79936</v>
+        <v>78985</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4755,21 +4755,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>410902</v>
+        <v>410935</v>
       </c>
       <c r="R43" t="n">
-        <v>6710163</v>
+        <v>6710081</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4841,10 +4841,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132197656</v>
+        <v>132197609</v>
       </c>
       <c r="B44" t="n">
-        <v>79317</v>
+        <v>79938</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4852,21 +4852,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4876,10 +4876,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>410938</v>
+        <v>410902</v>
       </c>
       <c r="R44" t="n">
-        <v>6710077</v>
+        <v>6710163</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4938,10 +4938,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132197600</v>
+        <v>132197656</v>
       </c>
       <c r="B45" t="n">
-        <v>78983</v>
+        <v>79319</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4949,21 +4949,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>410935</v>
+        <v>410938</v>
       </c>
       <c r="R45" t="n">
-        <v>6710081</v>
+        <v>6710077</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5038,7 +5038,7 @@
         <v>132197662</v>
       </c>
       <c r="B46" t="n">
-        <v>78983</v>
+        <v>78985</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>132197668</v>
       </c>
       <c r="B47" t="n">
-        <v>78983</v>
+        <v>78985</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>132197627</v>
       </c>
       <c r="B48" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>132197606</v>
       </c>
       <c r="B49" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5423,10 +5423,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132197629</v>
+        <v>132197628</v>
       </c>
       <c r="B50" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>410993</v>
+        <v>410998</v>
       </c>
       <c r="R50" t="n">
-        <v>6710175</v>
+        <v>6710174</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5520,10 +5520,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132197628</v>
+        <v>132197629</v>
       </c>
       <c r="B51" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5555,10 +5555,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>410998</v>
+        <v>410993</v>
       </c>
       <c r="R51" t="n">
-        <v>6710174</v>
+        <v>6710175</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5620,7 +5620,7 @@
         <v>132197604</v>
       </c>
       <c r="B52" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>132197661</v>
       </c>
       <c r="B53" t="n">
-        <v>78983</v>
+        <v>78985</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5811,10 +5811,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132197616</v>
+        <v>132197660</v>
       </c>
       <c r="B54" t="n">
-        <v>79936</v>
+        <v>78985</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5822,21 +5822,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>410952</v>
+        <v>410994</v>
       </c>
       <c r="R54" t="n">
-        <v>6710170</v>
+        <v>6710185</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5890,6 +5890,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5908,10 +5909,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132197660</v>
+        <v>132197616</v>
       </c>
       <c r="B55" t="n">
-        <v>78983</v>
+        <v>79938</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5919,21 +5920,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5943,10 +5944,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>410994</v>
+        <v>410952</v>
       </c>
       <c r="R55" t="n">
-        <v>6710185</v>
+        <v>6710170</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5987,7 +5988,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6009,7 +6009,7 @@
         <v>132197607</v>
       </c>
       <c r="B56" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>132197664</v>
       </c>
       <c r="B57" t="n">
-        <v>78983</v>
+        <v>78985</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 13525-2026 artfynd.xlsx
+++ b/artfynd/A 13525-2026 artfynd.xlsx
@@ -2123,32 +2123,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132197643</v>
+        <v>132197665</v>
       </c>
       <c r="B16" t="n">
-        <v>79343</v>
+        <v>78985</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>410998</v>
+        <v>410902</v>
       </c>
       <c r="R16" t="n">
         <v>6710163</v>
@@ -2220,32 +2220,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132197635</v>
+        <v>132197643</v>
       </c>
       <c r="B17" t="n">
-        <v>79938</v>
+        <v>79343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>410936</v>
+        <v>410998</v>
       </c>
       <c r="R17" t="n">
-        <v>6710017</v>
+        <v>6710163</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132197665</v>
+        <v>132197635</v>
       </c>
       <c r="B18" t="n">
-        <v>78985</v>
+        <v>79938</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>410902</v>
+        <v>410936</v>
       </c>
       <c r="R18" t="n">
-        <v>6710163</v>
+        <v>6710017</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>

--- a/artfynd/A 13525-2026 artfynd.xlsx
+++ b/artfynd/A 13525-2026 artfynd.xlsx
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132197630</v>
+        <v>132197648</v>
       </c>
       <c r="B8" t="n">
-        <v>79938</v>
+        <v>79085</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,21 +1358,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410994</v>
+        <v>410933</v>
       </c>
       <c r="R8" t="n">
-        <v>6710184</v>
+        <v>6710072</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132197619</v>
+        <v>132197663</v>
       </c>
       <c r="B9" t="n">
-        <v>79938</v>
+        <v>78993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,21 +1455,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>411038</v>
+        <v>410929</v>
       </c>
       <c r="R9" t="n">
-        <v>6710225</v>
+        <v>6710058</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,32 +1541,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132197663</v>
+        <v>132197640</v>
       </c>
       <c r="B10" t="n">
-        <v>78985</v>
+        <v>79413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6450</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>410929</v>
+        <v>410985</v>
       </c>
       <c r="R10" t="n">
-        <v>6710058</v>
+        <v>6710205</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1638,32 +1638,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132197640</v>
+        <v>132197619</v>
       </c>
       <c r="B11" t="n">
-        <v>79405</v>
+        <v>79946</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410985</v>
+        <v>411038</v>
       </c>
       <c r="R11" t="n">
-        <v>6710205</v>
+        <v>6710225</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132197648</v>
+        <v>132197630</v>
       </c>
       <c r="B12" t="n">
-        <v>79077</v>
+        <v>79946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410933</v>
+        <v>410994</v>
       </c>
       <c r="R12" t="n">
-        <v>6710072</v>
+        <v>6710184</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1835,7 +1835,7 @@
         <v>132197669</v>
       </c>
       <c r="B13" t="n">
-        <v>78985</v>
+        <v>78993</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>132197666</v>
       </c>
       <c r="B14" t="n">
-        <v>78985</v>
+        <v>78993</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>132197601</v>
       </c>
       <c r="B15" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2123,32 +2123,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132197665</v>
+        <v>132197643</v>
       </c>
       <c r="B16" t="n">
-        <v>78985</v>
+        <v>79351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>410902</v>
+        <v>410998</v>
       </c>
       <c r="R16" t="n">
         <v>6710163</v>
@@ -2220,32 +2220,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132197643</v>
+        <v>132197635</v>
       </c>
       <c r="B17" t="n">
-        <v>79343</v>
+        <v>79946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>410998</v>
+        <v>410936</v>
       </c>
       <c r="R17" t="n">
-        <v>6710163</v>
+        <v>6710017</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132197635</v>
+        <v>132197665</v>
       </c>
       <c r="B18" t="n">
-        <v>79938</v>
+        <v>78993</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>410936</v>
+        <v>410902</v>
       </c>
       <c r="R18" t="n">
-        <v>6710017</v>
+        <v>6710163</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132197671</v>
+        <v>132197670</v>
       </c>
       <c r="B19" t="n">
-        <v>78985</v>
+        <v>78993</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>410977</v>
+        <v>410995</v>
       </c>
       <c r="R19" t="n">
-        <v>6710177</v>
+        <v>6710181</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132197670</v>
+        <v>132197671</v>
       </c>
       <c r="B20" t="n">
-        <v>78985</v>
+        <v>78993</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>410995</v>
+        <v>410977</v>
       </c>
       <c r="R20" t="n">
-        <v>6710181</v>
+        <v>6710177</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2608,10 +2608,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132197631</v>
+        <v>132197652</v>
       </c>
       <c r="B21" t="n">
-        <v>79938</v>
+        <v>79085</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,21 +2619,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>410991</v>
+        <v>410937</v>
       </c>
       <c r="R21" t="n">
-        <v>6710191</v>
+        <v>6710017</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2705,10 +2705,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132197608</v>
+        <v>132197651</v>
       </c>
       <c r="B22" t="n">
-        <v>79938</v>
+        <v>79085</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2716,21 +2716,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>410931</v>
+        <v>411000</v>
       </c>
       <c r="R22" t="n">
-        <v>6710096</v>
+        <v>6710007</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2805,7 +2805,7 @@
         <v>132197633</v>
       </c>
       <c r="B23" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132197652</v>
+        <v>132197631</v>
       </c>
       <c r="B24" t="n">
-        <v>79077</v>
+        <v>79946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2910,21 +2910,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410937</v>
+        <v>410991</v>
       </c>
       <c r="R24" t="n">
-        <v>6710017</v>
+        <v>6710191</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2996,10 +2996,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132197651</v>
+        <v>132197608</v>
       </c>
       <c r="B25" t="n">
-        <v>79077</v>
+        <v>79946</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3007,21 +3007,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>411000</v>
+        <v>410931</v>
       </c>
       <c r="R25" t="n">
-        <v>6710007</v>
+        <v>6710096</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3093,10 +3093,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132197602</v>
+        <v>132197654</v>
       </c>
       <c r="B26" t="n">
-        <v>79938</v>
+        <v>79084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3104,21 +3104,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410973</v>
+        <v>410960</v>
       </c>
       <c r="R26" t="n">
-        <v>6709995</v>
+        <v>6710167</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3190,10 +3190,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132197654</v>
+        <v>132197602</v>
       </c>
       <c r="B27" t="n">
-        <v>79076</v>
+        <v>79946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3201,21 +3201,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>410960</v>
+        <v>410973</v>
       </c>
       <c r="R27" t="n">
-        <v>6710167</v>
+        <v>6709995</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3290,7 +3290,7 @@
         <v>132197644</v>
       </c>
       <c r="B28" t="n">
-        <v>79343</v>
+        <v>79351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>132197636</v>
       </c>
       <c r="B29" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>132197637</v>
       </c>
       <c r="B30" t="n">
-        <v>79909</v>
+        <v>79917</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>132197667</v>
       </c>
       <c r="B31" t="n">
-        <v>78985</v>
+        <v>78993</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132197615</v>
+        <v>132197605</v>
       </c>
       <c r="B32" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>410939</v>
+        <v>410950</v>
       </c>
       <c r="R32" t="n">
-        <v>6710183</v>
+        <v>6709984</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3772,10 +3772,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132197605</v>
+        <v>132197615</v>
       </c>
       <c r="B33" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>410950</v>
+        <v>410939</v>
       </c>
       <c r="R33" t="n">
-        <v>6709984</v>
+        <v>6710183</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3872,7 +3872,7 @@
         <v>132197647</v>
       </c>
       <c r="B34" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>132197653</v>
       </c>
       <c r="B35" t="n">
-        <v>81304</v>
+        <v>81312</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>132197659</v>
       </c>
       <c r="B36" t="n">
-        <v>78985</v>
+        <v>78993</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132197646</v>
+        <v>132197655</v>
       </c>
       <c r="B37" t="n">
-        <v>79077</v>
+        <v>79084</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>410983</v>
+        <v>411091</v>
       </c>
       <c r="R37" t="n">
-        <v>6709997</v>
+        <v>6710283</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4240,6 +4240,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4258,10 +4259,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132197650</v>
+        <v>132197646</v>
       </c>
       <c r="B38" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4293,10 +4294,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>410986</v>
+        <v>410983</v>
       </c>
       <c r="R38" t="n">
-        <v>6710178</v>
+        <v>6709997</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4355,10 +4356,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132197655</v>
+        <v>132197650</v>
       </c>
       <c r="B39" t="n">
-        <v>79076</v>
+        <v>79085</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4366,21 +4367,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4390,10 +4391,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>411091</v>
+        <v>410986</v>
       </c>
       <c r="R39" t="n">
-        <v>6710283</v>
+        <v>6710178</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4434,7 +4435,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4456,7 +4456,7 @@
         <v>132197618</v>
       </c>
       <c r="B40" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4550,10 +4550,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132197634</v>
+        <v>132197632</v>
       </c>
       <c r="B41" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4585,10 +4585,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>410980</v>
+        <v>410998</v>
       </c>
       <c r="R41" t="n">
-        <v>6710008</v>
+        <v>6710163</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4647,10 +4647,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132197632</v>
+        <v>132197634</v>
       </c>
       <c r="B42" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4682,10 +4682,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>410998</v>
+        <v>410980</v>
       </c>
       <c r="R42" t="n">
-        <v>6710163</v>
+        <v>6710008</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4744,10 +4744,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132197600</v>
+        <v>132197609</v>
       </c>
       <c r="B43" t="n">
-        <v>78985</v>
+        <v>79946</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4755,21 +4755,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>410935</v>
+        <v>410902</v>
       </c>
       <c r="R43" t="n">
-        <v>6710081</v>
+        <v>6710163</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4841,10 +4841,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132197609</v>
+        <v>132197600</v>
       </c>
       <c r="B44" t="n">
-        <v>79938</v>
+        <v>78993</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4852,21 +4852,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4876,10 +4876,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>410902</v>
+        <v>410935</v>
       </c>
       <c r="R44" t="n">
-        <v>6710163</v>
+        <v>6710081</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4941,7 +4941,7 @@
         <v>132197656</v>
       </c>
       <c r="B45" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>132197662</v>
       </c>
       <c r="B46" t="n">
-        <v>78985</v>
+        <v>78993</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>132197668</v>
       </c>
       <c r="B47" t="n">
-        <v>78985</v>
+        <v>78993</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>132197627</v>
       </c>
       <c r="B48" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>132197606</v>
       </c>
       <c r="B49" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5423,10 +5423,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132197628</v>
+        <v>132197629</v>
       </c>
       <c r="B50" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>410998</v>
+        <v>410993</v>
       </c>
       <c r="R50" t="n">
-        <v>6710174</v>
+        <v>6710175</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5520,10 +5520,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132197629</v>
+        <v>132197628</v>
       </c>
       <c r="B51" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5555,10 +5555,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>410993</v>
+        <v>410998</v>
       </c>
       <c r="R51" t="n">
-        <v>6710175</v>
+        <v>6710174</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5620,7 +5620,7 @@
         <v>132197604</v>
       </c>
       <c r="B52" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>132197661</v>
       </c>
       <c r="B53" t="n">
-        <v>78985</v>
+        <v>78993</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5811,10 +5811,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132197660</v>
+        <v>132197616</v>
       </c>
       <c r="B54" t="n">
-        <v>78985</v>
+        <v>79946</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5822,21 +5822,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>410994</v>
+        <v>410952</v>
       </c>
       <c r="R54" t="n">
-        <v>6710185</v>
+        <v>6710170</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5890,7 +5890,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5909,10 +5908,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132197616</v>
+        <v>132197660</v>
       </c>
       <c r="B55" t="n">
-        <v>79938</v>
+        <v>78993</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5920,21 +5919,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5944,10 +5943,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>410952</v>
+        <v>410994</v>
       </c>
       <c r="R55" t="n">
-        <v>6710170</v>
+        <v>6710185</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5988,6 +5987,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6009,7 +6009,7 @@
         <v>132197607</v>
       </c>
       <c r="B56" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>132197664</v>
       </c>
       <c r="B57" t="n">
-        <v>78985</v>
+        <v>78993</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 13525-2026 artfynd.xlsx
+++ b/artfynd/A 13525-2026 artfynd.xlsx
@@ -2608,10 +2608,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132197652</v>
+        <v>132197633</v>
       </c>
       <c r="B21" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,21 +2619,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>410937</v>
+        <v>410961</v>
       </c>
       <c r="R21" t="n">
-        <v>6710017</v>
+        <v>6710167</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2705,10 +2705,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132197651</v>
+        <v>132197631</v>
       </c>
       <c r="B22" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2716,21 +2716,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>411000</v>
+        <v>410991</v>
       </c>
       <c r="R22" t="n">
-        <v>6710007</v>
+        <v>6710191</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2802,7 +2802,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132197633</v>
+        <v>132197608</v>
       </c>
       <c r="B23" t="n">
         <v>79946</v>
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410961</v>
+        <v>410931</v>
       </c>
       <c r="R23" t="n">
-        <v>6710167</v>
+        <v>6710096</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132197631</v>
+        <v>132197652</v>
       </c>
       <c r="B24" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2910,21 +2910,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410991</v>
+        <v>410937</v>
       </c>
       <c r="R24" t="n">
-        <v>6710191</v>
+        <v>6710017</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2996,10 +2996,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132197608</v>
+        <v>132197651</v>
       </c>
       <c r="B25" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3007,21 +3007,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410931</v>
+        <v>411000</v>
       </c>
       <c r="R25" t="n">
-        <v>6710096</v>
+        <v>6710007</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132197667</v>
+        <v>132197647</v>
       </c>
       <c r="B31" t="n">
-        <v>78993</v>
+        <v>79085</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>411027</v>
+        <v>410950</v>
       </c>
       <c r="R31" t="n">
-        <v>6710222</v>
+        <v>6709984</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132197605</v>
+        <v>132197667</v>
       </c>
       <c r="B32" t="n">
-        <v>79946</v>
+        <v>78993</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3686,21 +3686,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>410950</v>
+        <v>411027</v>
       </c>
       <c r="R32" t="n">
-        <v>6709984</v>
+        <v>6710222</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3772,7 +3772,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132197615</v>
+        <v>132197605</v>
       </c>
       <c r="B33" t="n">
         <v>79946</v>
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>410939</v>
+        <v>410950</v>
       </c>
       <c r="R33" t="n">
-        <v>6710183</v>
+        <v>6709984</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3869,10 +3869,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132197647</v>
+        <v>132197615</v>
       </c>
       <c r="B34" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3880,21 +3880,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>410950</v>
+        <v>410939</v>
       </c>
       <c r="R34" t="n">
-        <v>6709984</v>
+        <v>6710183</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132197653</v>
+        <v>132197655</v>
       </c>
       <c r="B35" t="n">
-        <v>81312</v>
+        <v>79084</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3977,21 +3977,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>410972</v>
+        <v>411091</v>
       </c>
       <c r="R35" t="n">
-        <v>6710194</v>
+        <v>6710283</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4045,6 +4045,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4063,10 +4064,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132197659</v>
+        <v>132197653</v>
       </c>
       <c r="B36" t="n">
-        <v>78993</v>
+        <v>81312</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4074,21 +4075,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4098,10 +4099,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>410973</v>
+        <v>410972</v>
       </c>
       <c r="R36" t="n">
-        <v>6709994</v>
+        <v>6710194</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4142,7 +4143,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132197655</v>
+        <v>132197659</v>
       </c>
       <c r="B37" t="n">
-        <v>79084</v>
+        <v>78993</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>411091</v>
+        <v>410973</v>
       </c>
       <c r="R37" t="n">
-        <v>6710283</v>
+        <v>6709994</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4744,10 +4744,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132197609</v>
+        <v>132197600</v>
       </c>
       <c r="B43" t="n">
-        <v>79946</v>
+        <v>78993</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4755,21 +4755,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>410902</v>
+        <v>410935</v>
       </c>
       <c r="R43" t="n">
-        <v>6710163</v>
+        <v>6710081</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4841,10 +4841,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132197600</v>
+        <v>132197656</v>
       </c>
       <c r="B44" t="n">
-        <v>78993</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4852,21 +4852,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4876,10 +4876,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>410935</v>
+        <v>410938</v>
       </c>
       <c r="R44" t="n">
-        <v>6710081</v>
+        <v>6710077</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4938,10 +4938,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132197656</v>
+        <v>132197609</v>
       </c>
       <c r="B45" t="n">
-        <v>79327</v>
+        <v>79946</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4949,21 +4949,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>410938</v>
+        <v>410902</v>
       </c>
       <c r="R45" t="n">
-        <v>6710077</v>
+        <v>6710163</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5811,10 +5811,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132197616</v>
+        <v>132197660</v>
       </c>
       <c r="B54" t="n">
-        <v>79946</v>
+        <v>78993</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5822,21 +5822,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>410952</v>
+        <v>410994</v>
       </c>
       <c r="R54" t="n">
-        <v>6710170</v>
+        <v>6710185</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5890,6 +5890,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5908,10 +5909,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132197660</v>
+        <v>132197616</v>
       </c>
       <c r="B55" t="n">
-        <v>78993</v>
+        <v>79946</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5919,21 +5920,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5943,10 +5944,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>410994</v>
+        <v>410952</v>
       </c>
       <c r="R55" t="n">
-        <v>6710185</v>
+        <v>6710170</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5987,7 +5988,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6006,10 +6006,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132197607</v>
+        <v>132197664</v>
       </c>
       <c r="B56" t="n">
-        <v>79946</v>
+        <v>78993</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6017,21 +6017,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>410933</v>
+        <v>410928</v>
       </c>
       <c r="R56" t="n">
-        <v>6710072</v>
+        <v>6710090</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6103,10 +6103,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132197664</v>
+        <v>132197607</v>
       </c>
       <c r="B57" t="n">
-        <v>78993</v>
+        <v>79946</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6114,21 +6114,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6138,10 +6138,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>410928</v>
+        <v>410933</v>
       </c>
       <c r="R57" t="n">
-        <v>6710090</v>
+        <v>6710072</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>

--- a/artfynd/A 13525-2026 artfynd.xlsx
+++ b/artfynd/A 13525-2026 artfynd.xlsx
@@ -1347,32 +1347,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132197648</v>
+        <v>132197640</v>
       </c>
       <c r="B8" t="n">
-        <v>79085</v>
+        <v>79413</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6450</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410933</v>
+        <v>410985</v>
       </c>
       <c r="R8" t="n">
-        <v>6710072</v>
+        <v>6710205</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132197663</v>
+        <v>132197619</v>
       </c>
       <c r="B9" t="n">
-        <v>78993</v>
+        <v>79946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,21 +1455,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>410929</v>
+        <v>411038</v>
       </c>
       <c r="R9" t="n">
-        <v>6710058</v>
+        <v>6710225</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,32 +1541,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132197640</v>
+        <v>132197630</v>
       </c>
       <c r="B10" t="n">
-        <v>79413</v>
+        <v>79946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>410985</v>
+        <v>410994</v>
       </c>
       <c r="R10" t="n">
-        <v>6710205</v>
+        <v>6710184</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132197619</v>
+        <v>132197663</v>
       </c>
       <c r="B11" t="n">
-        <v>79946</v>
+        <v>78993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>411038</v>
+        <v>410929</v>
       </c>
       <c r="R11" t="n">
-        <v>6710225</v>
+        <v>6710058</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132197630</v>
+        <v>132197648</v>
       </c>
       <c r="B12" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410994</v>
+        <v>410933</v>
       </c>
       <c r="R12" t="n">
-        <v>6710184</v>
+        <v>6710072</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2123,32 +2123,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132197643</v>
+        <v>132197665</v>
       </c>
       <c r="B16" t="n">
-        <v>79351</v>
+        <v>78993</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>410998</v>
+        <v>410902</v>
       </c>
       <c r="R16" t="n">
         <v>6710163</v>
@@ -2220,32 +2220,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132197635</v>
+        <v>132197643</v>
       </c>
       <c r="B17" t="n">
-        <v>79946</v>
+        <v>79351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>410936</v>
+        <v>410998</v>
       </c>
       <c r="R17" t="n">
-        <v>6710017</v>
+        <v>6710163</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132197665</v>
+        <v>132197635</v>
       </c>
       <c r="B18" t="n">
-        <v>78993</v>
+        <v>79946</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>410902</v>
+        <v>410936</v>
       </c>
       <c r="R18" t="n">
-        <v>6710163</v>
+        <v>6710017</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132197647</v>
+        <v>132197605</v>
       </c>
       <c r="B31" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132197667</v>
+        <v>132197615</v>
       </c>
       <c r="B32" t="n">
-        <v>78993</v>
+        <v>79946</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3686,21 +3686,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>411027</v>
+        <v>410939</v>
       </c>
       <c r="R32" t="n">
-        <v>6710222</v>
+        <v>6710183</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3772,10 +3772,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132197605</v>
+        <v>132197667</v>
       </c>
       <c r="B33" t="n">
-        <v>79946</v>
+        <v>78993</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3783,21 +3783,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>410950</v>
+        <v>411027</v>
       </c>
       <c r="R33" t="n">
-        <v>6709984</v>
+        <v>6710222</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3869,10 +3869,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132197615</v>
+        <v>132197647</v>
       </c>
       <c r="B34" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3880,21 +3880,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>410939</v>
+        <v>410950</v>
       </c>
       <c r="R34" t="n">
-        <v>6710183</v>
+        <v>6709984</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132197655</v>
+        <v>132197646</v>
       </c>
       <c r="B35" t="n">
-        <v>79084</v>
+        <v>79085</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3977,21 +3977,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>411091</v>
+        <v>410983</v>
       </c>
       <c r="R35" t="n">
-        <v>6710283</v>
+        <v>6709997</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4045,7 +4045,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4064,10 +4063,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132197653</v>
+        <v>132197650</v>
       </c>
       <c r="B36" t="n">
-        <v>81312</v>
+        <v>79085</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,21 +4074,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4099,10 +4098,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>410972</v>
+        <v>410986</v>
       </c>
       <c r="R36" t="n">
-        <v>6710194</v>
+        <v>6710178</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4161,10 +4160,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132197659</v>
+        <v>132197653</v>
       </c>
       <c r="B37" t="n">
-        <v>78993</v>
+        <v>81312</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4172,21 +4171,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4196,10 +4195,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>410973</v>
+        <v>410972</v>
       </c>
       <c r="R37" t="n">
-        <v>6709994</v>
+        <v>6710194</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4240,7 +4239,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4259,10 +4257,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132197646</v>
+        <v>132197659</v>
       </c>
       <c r="B38" t="n">
-        <v>79085</v>
+        <v>78993</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4270,21 +4268,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4294,10 +4292,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>410983</v>
+        <v>410973</v>
       </c>
       <c r="R38" t="n">
-        <v>6709997</v>
+        <v>6709994</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4338,6 +4336,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4356,10 +4355,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132197650</v>
+        <v>132197655</v>
       </c>
       <c r="B39" t="n">
-        <v>79085</v>
+        <v>79084</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4367,21 +4366,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4391,10 +4390,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>410986</v>
+        <v>411091</v>
       </c>
       <c r="R39" t="n">
-        <v>6710178</v>
+        <v>6710283</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4435,6 +4434,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4744,10 +4744,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132197600</v>
+        <v>132197609</v>
       </c>
       <c r="B43" t="n">
-        <v>78993</v>
+        <v>79946</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4755,21 +4755,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>410935</v>
+        <v>410902</v>
       </c>
       <c r="R43" t="n">
-        <v>6710081</v>
+        <v>6710163</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4938,10 +4938,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132197609</v>
+        <v>132197600</v>
       </c>
       <c r="B45" t="n">
-        <v>79946</v>
+        <v>78993</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4949,21 +4949,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>410902</v>
+        <v>410935</v>
       </c>
       <c r="R45" t="n">
-        <v>6710163</v>
+        <v>6710081</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5132,10 +5132,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132197668</v>
+        <v>132197627</v>
       </c>
       <c r="B47" t="n">
-        <v>78993</v>
+        <v>79946</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5143,21 +5143,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>411097</v>
+        <v>410971</v>
       </c>
       <c r="R47" t="n">
-        <v>6710289</v>
+        <v>6710196</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5229,7 +5229,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132197627</v>
+        <v>132197606</v>
       </c>
       <c r="B48" t="n">
         <v>79946</v>
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>410971</v>
+        <v>410946</v>
       </c>
       <c r="R48" t="n">
-        <v>6710196</v>
+        <v>6709981</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5326,10 +5326,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132197606</v>
+        <v>132197668</v>
       </c>
       <c r="B49" t="n">
-        <v>79946</v>
+        <v>78993</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5337,21 +5337,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5361,10 +5361,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>410946</v>
+        <v>411097</v>
       </c>
       <c r="R49" t="n">
-        <v>6709981</v>
+        <v>6710289</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5811,10 +5811,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132197660</v>
+        <v>132197616</v>
       </c>
       <c r="B54" t="n">
-        <v>78993</v>
+        <v>79946</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5822,21 +5822,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>410994</v>
+        <v>410952</v>
       </c>
       <c r="R54" t="n">
-        <v>6710185</v>
+        <v>6710170</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5890,7 +5890,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5909,10 +5908,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132197616</v>
+        <v>132197660</v>
       </c>
       <c r="B55" t="n">
-        <v>79946</v>
+        <v>78993</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5920,21 +5919,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5944,10 +5943,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>410952</v>
+        <v>410994</v>
       </c>
       <c r="R55" t="n">
-        <v>6710170</v>
+        <v>6710185</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5988,6 +5987,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6006,10 +6006,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132197664</v>
+        <v>132197607</v>
       </c>
       <c r="B56" t="n">
-        <v>78993</v>
+        <v>79946</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6017,21 +6017,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>410928</v>
+        <v>410933</v>
       </c>
       <c r="R56" t="n">
-        <v>6710090</v>
+        <v>6710072</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6103,10 +6103,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132197607</v>
+        <v>132197664</v>
       </c>
       <c r="B57" t="n">
-        <v>79946</v>
+        <v>78993</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6114,21 +6114,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6138,10 +6138,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>410933</v>
+        <v>410928</v>
       </c>
       <c r="R57" t="n">
-        <v>6710072</v>
+        <v>6710090</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>

--- a/artfynd/A 13525-2026 artfynd.xlsx
+++ b/artfynd/A 13525-2026 artfynd.xlsx
@@ -1347,32 +1347,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132197640</v>
+        <v>132197648</v>
       </c>
       <c r="B8" t="n">
-        <v>79413</v>
+        <v>79085</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6450</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410985</v>
+        <v>410933</v>
       </c>
       <c r="R8" t="n">
-        <v>6710205</v>
+        <v>6710072</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1444,32 +1444,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132197619</v>
+        <v>132197640</v>
       </c>
       <c r="B9" t="n">
-        <v>79946</v>
+        <v>79413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6450</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>411038</v>
+        <v>410985</v>
       </c>
       <c r="R9" t="n">
-        <v>6710225</v>
+        <v>6710205</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132197630</v>
+        <v>132197619</v>
       </c>
       <c r="B10" t="n">
         <v>79946</v>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>410994</v>
+        <v>411038</v>
       </c>
       <c r="R10" t="n">
-        <v>6710184</v>
+        <v>6710225</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132197663</v>
+        <v>132197630</v>
       </c>
       <c r="B11" t="n">
-        <v>78993</v>
+        <v>79946</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410929</v>
+        <v>410994</v>
       </c>
       <c r="R11" t="n">
-        <v>6710058</v>
+        <v>6710184</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132197648</v>
+        <v>132197663</v>
       </c>
       <c r="B12" t="n">
-        <v>79085</v>
+        <v>78993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410933</v>
+        <v>410929</v>
       </c>
       <c r="R12" t="n">
-        <v>6710072</v>
+        <v>6710058</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132197669</v>
+        <v>132197601</v>
       </c>
       <c r="B13" t="n">
-        <v>78993</v>
+        <v>79946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,21 +1843,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>410992</v>
+        <v>410984</v>
       </c>
       <c r="R13" t="n">
-        <v>6710219</v>
+        <v>6709997</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132197666</v>
+        <v>132197669</v>
       </c>
       <c r="B14" t="n">
         <v>78993</v>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>410952</v>
+        <v>410992</v>
       </c>
       <c r="R14" t="n">
-        <v>6710169</v>
+        <v>6710219</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2026,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132197601</v>
+        <v>132197666</v>
       </c>
       <c r="B15" t="n">
-        <v>79946</v>
+        <v>78993</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>410984</v>
+        <v>410952</v>
       </c>
       <c r="R15" t="n">
-        <v>6709997</v>
+        <v>6710169</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -3772,10 +3772,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132197667</v>
+        <v>132197647</v>
       </c>
       <c r="B33" t="n">
-        <v>78993</v>
+        <v>79085</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3783,21 +3783,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>411027</v>
+        <v>410950</v>
       </c>
       <c r="R33" t="n">
-        <v>6710222</v>
+        <v>6709984</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3869,10 +3869,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132197647</v>
+        <v>132197667</v>
       </c>
       <c r="B34" t="n">
-        <v>79085</v>
+        <v>78993</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3880,21 +3880,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>410950</v>
+        <v>411027</v>
       </c>
       <c r="R34" t="n">
-        <v>6709984</v>
+        <v>6710222</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132197646</v>
+        <v>132197655</v>
       </c>
       <c r="B35" t="n">
-        <v>79085</v>
+        <v>79084</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3977,21 +3977,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>410983</v>
+        <v>411091</v>
       </c>
       <c r="R35" t="n">
-        <v>6709997</v>
+        <v>6710283</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4045,6 +4045,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4063,10 +4064,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132197650</v>
+        <v>132197653</v>
       </c>
       <c r="B36" t="n">
-        <v>79085</v>
+        <v>81312</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4074,21 +4075,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4098,10 +4099,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>410986</v>
+        <v>410972</v>
       </c>
       <c r="R36" t="n">
-        <v>6710178</v>
+        <v>6710194</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4160,10 +4161,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132197653</v>
+        <v>132197659</v>
       </c>
       <c r="B37" t="n">
-        <v>81312</v>
+        <v>78993</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4171,21 +4172,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4195,10 +4196,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>410972</v>
+        <v>410973</v>
       </c>
       <c r="R37" t="n">
-        <v>6710194</v>
+        <v>6709994</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4239,6 +4240,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4257,10 +4259,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132197659</v>
+        <v>132197646</v>
       </c>
       <c r="B38" t="n">
-        <v>78993</v>
+        <v>79085</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4268,21 +4270,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4292,10 +4294,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>410973</v>
+        <v>410983</v>
       </c>
       <c r="R38" t="n">
-        <v>6709994</v>
+        <v>6709997</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4336,7 +4338,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4355,10 +4356,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132197655</v>
+        <v>132197650</v>
       </c>
       <c r="B39" t="n">
-        <v>79084</v>
+        <v>79085</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4366,21 +4367,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4390,10 +4391,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>411091</v>
+        <v>410986</v>
       </c>
       <c r="R39" t="n">
-        <v>6710283</v>
+        <v>6710178</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4434,7 +4435,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13525-2026 artfynd.xlsx
+++ b/artfynd/A 13525-2026 artfynd.xlsx
@@ -1444,32 +1444,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132197640</v>
+        <v>132197663</v>
       </c>
       <c r="B9" t="n">
-        <v>79413</v>
+        <v>78993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6450</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>410985</v>
+        <v>410929</v>
       </c>
       <c r="R9" t="n">
-        <v>6710205</v>
+        <v>6710058</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,32 +1541,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132197619</v>
+        <v>132197640</v>
       </c>
       <c r="B10" t="n">
-        <v>79946</v>
+        <v>79413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6450</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>411038</v>
+        <v>410985</v>
       </c>
       <c r="R10" t="n">
-        <v>6710225</v>
+        <v>6710205</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132197630</v>
+        <v>132197619</v>
       </c>
       <c r="B11" t="n">
         <v>79946</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410994</v>
+        <v>411038</v>
       </c>
       <c r="R11" t="n">
-        <v>6710184</v>
+        <v>6710225</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132197663</v>
+        <v>132197630</v>
       </c>
       <c r="B12" t="n">
-        <v>78993</v>
+        <v>79946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410929</v>
+        <v>410994</v>
       </c>
       <c r="R12" t="n">
-        <v>6710058</v>
+        <v>6710184</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132197601</v>
+        <v>132197669</v>
       </c>
       <c r="B13" t="n">
-        <v>79946</v>
+        <v>78993</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,21 +1843,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>410984</v>
+        <v>410992</v>
       </c>
       <c r="R13" t="n">
-        <v>6709997</v>
+        <v>6710219</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132197669</v>
+        <v>132197666</v>
       </c>
       <c r="B14" t="n">
         <v>78993</v>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>410992</v>
+        <v>410952</v>
       </c>
       <c r="R14" t="n">
-        <v>6710219</v>
+        <v>6710169</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2026,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132197666</v>
+        <v>132197601</v>
       </c>
       <c r="B15" t="n">
-        <v>78993</v>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>410952</v>
+        <v>410984</v>
       </c>
       <c r="R15" t="n">
-        <v>6710169</v>
+        <v>6709997</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2123,32 +2123,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132197665</v>
+        <v>132197643</v>
       </c>
       <c r="B16" t="n">
-        <v>78993</v>
+        <v>79351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>410902</v>
+        <v>410998</v>
       </c>
       <c r="R16" t="n">
         <v>6710163</v>
@@ -2220,32 +2220,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132197643</v>
+        <v>132197635</v>
       </c>
       <c r="B17" t="n">
-        <v>79351</v>
+        <v>79946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>410998</v>
+        <v>410936</v>
       </c>
       <c r="R17" t="n">
-        <v>6710163</v>
+        <v>6710017</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132197635</v>
+        <v>132197665</v>
       </c>
       <c r="B18" t="n">
-        <v>79946</v>
+        <v>78993</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>410936</v>
+        <v>410902</v>
       </c>
       <c r="R18" t="n">
-        <v>6710017</v>
+        <v>6710163</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2608,10 +2608,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132197633</v>
+        <v>132197652</v>
       </c>
       <c r="B21" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,21 +2619,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>410961</v>
+        <v>410937</v>
       </c>
       <c r="R21" t="n">
-        <v>6710167</v>
+        <v>6710017</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2705,10 +2705,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132197631</v>
+        <v>132197651</v>
       </c>
       <c r="B22" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2716,21 +2716,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>410991</v>
+        <v>411000</v>
       </c>
       <c r="R22" t="n">
-        <v>6710191</v>
+        <v>6710007</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2802,7 +2802,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132197608</v>
+        <v>132197633</v>
       </c>
       <c r="B23" t="n">
         <v>79946</v>
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410931</v>
+        <v>410961</v>
       </c>
       <c r="R23" t="n">
-        <v>6710096</v>
+        <v>6710167</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132197652</v>
+        <v>132197631</v>
       </c>
       <c r="B24" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2910,21 +2910,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410937</v>
+        <v>410991</v>
       </c>
       <c r="R24" t="n">
-        <v>6710017</v>
+        <v>6710191</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2996,10 +2996,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132197651</v>
+        <v>132197608</v>
       </c>
       <c r="B25" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3007,21 +3007,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>411000</v>
+        <v>410931</v>
       </c>
       <c r="R25" t="n">
-        <v>6710007</v>
+        <v>6710096</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132197605</v>
+        <v>132197667</v>
       </c>
       <c r="B31" t="n">
-        <v>79946</v>
+        <v>78993</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>410950</v>
+        <v>411027</v>
       </c>
       <c r="R31" t="n">
-        <v>6709984</v>
+        <v>6710222</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3675,7 +3675,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132197615</v>
+        <v>132197605</v>
       </c>
       <c r="B32" t="n">
         <v>79946</v>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>410939</v>
+        <v>410950</v>
       </c>
       <c r="R32" t="n">
-        <v>6710183</v>
+        <v>6709984</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3772,10 +3772,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132197647</v>
+        <v>132197615</v>
       </c>
       <c r="B33" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3783,21 +3783,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>410950</v>
+        <v>410939</v>
       </c>
       <c r="R33" t="n">
-        <v>6709984</v>
+        <v>6710183</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3869,10 +3869,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132197667</v>
+        <v>132197647</v>
       </c>
       <c r="B34" t="n">
-        <v>78993</v>
+        <v>79085</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3880,21 +3880,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>411027</v>
+        <v>410950</v>
       </c>
       <c r="R34" t="n">
-        <v>6710222</v>
+        <v>6709984</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132197655</v>
+        <v>132197653</v>
       </c>
       <c r="B35" t="n">
-        <v>79084</v>
+        <v>81312</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3977,21 +3977,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>411091</v>
+        <v>410972</v>
       </c>
       <c r="R35" t="n">
-        <v>6710283</v>
+        <v>6710194</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4045,7 +4045,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4064,10 +4063,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132197653</v>
+        <v>132197659</v>
       </c>
       <c r="B36" t="n">
-        <v>81312</v>
+        <v>78993</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,21 +4074,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4099,10 +4098,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>410972</v>
+        <v>410973</v>
       </c>
       <c r="R36" t="n">
-        <v>6710194</v>
+        <v>6709994</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4143,6 +4142,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132197659</v>
+        <v>132197655</v>
       </c>
       <c r="B37" t="n">
-        <v>78993</v>
+        <v>79084</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>410973</v>
+        <v>411091</v>
       </c>
       <c r="R37" t="n">
-        <v>6709994</v>
+        <v>6710283</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4744,10 +4744,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132197609</v>
+        <v>132197600</v>
       </c>
       <c r="B43" t="n">
-        <v>79946</v>
+        <v>78993</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4755,21 +4755,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>410902</v>
+        <v>410935</v>
       </c>
       <c r="R43" t="n">
-        <v>6710163</v>
+        <v>6710081</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4841,10 +4841,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132197656</v>
+        <v>132197609</v>
       </c>
       <c r="B44" t="n">
-        <v>79327</v>
+        <v>79946</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4852,21 +4852,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4876,10 +4876,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>410938</v>
+        <v>410902</v>
       </c>
       <c r="R44" t="n">
-        <v>6710077</v>
+        <v>6710163</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4938,10 +4938,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132197600</v>
+        <v>132197656</v>
       </c>
       <c r="B45" t="n">
-        <v>78993</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4949,21 +4949,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>410935</v>
+        <v>410938</v>
       </c>
       <c r="R45" t="n">
-        <v>6710081</v>
+        <v>6710077</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5811,10 +5811,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132197616</v>
+        <v>132197660</v>
       </c>
       <c r="B54" t="n">
-        <v>79946</v>
+        <v>78993</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5822,21 +5822,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>410952</v>
+        <v>410994</v>
       </c>
       <c r="R54" t="n">
-        <v>6710170</v>
+        <v>6710185</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5890,6 +5890,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5908,10 +5909,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132197660</v>
+        <v>132197616</v>
       </c>
       <c r="B55" t="n">
-        <v>78993</v>
+        <v>79946</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5919,21 +5920,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5943,10 +5944,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>410994</v>
+        <v>410952</v>
       </c>
       <c r="R55" t="n">
-        <v>6710185</v>
+        <v>6710170</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5987,7 +5988,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6006,10 +6006,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132197607</v>
+        <v>132197664</v>
       </c>
       <c r="B56" t="n">
-        <v>79946</v>
+        <v>78993</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6017,21 +6017,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>410933</v>
+        <v>410928</v>
       </c>
       <c r="R56" t="n">
-        <v>6710072</v>
+        <v>6710090</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6103,10 +6103,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132197664</v>
+        <v>132197607</v>
       </c>
       <c r="B57" t="n">
-        <v>78993</v>
+        <v>79946</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6114,21 +6114,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6138,10 +6138,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>410928</v>
+        <v>410933</v>
       </c>
       <c r="R57" t="n">
-        <v>6710090</v>
+        <v>6710072</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>

--- a/artfynd/A 13525-2026 artfynd.xlsx
+++ b/artfynd/A 13525-2026 artfynd.xlsx
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132197648</v>
+        <v>132197663</v>
       </c>
       <c r="B8" t="n">
-        <v>79085</v>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,21 +1358,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410933</v>
+        <v>410929</v>
       </c>
       <c r="R8" t="n">
-        <v>6710072</v>
+        <v>6710058</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1444,32 +1444,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132197663</v>
+        <v>132197640</v>
       </c>
       <c r="B9" t="n">
-        <v>78993</v>
+        <v>79413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6450</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>410929</v>
+        <v>410985</v>
       </c>
       <c r="R9" t="n">
-        <v>6710058</v>
+        <v>6710205</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,32 +1541,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132197640</v>
+        <v>132197619</v>
       </c>
       <c r="B10" t="n">
-        <v>79413</v>
+        <v>79946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>410985</v>
+        <v>411038</v>
       </c>
       <c r="R10" t="n">
-        <v>6710205</v>
+        <v>6710225</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132197619</v>
+        <v>132197630</v>
       </c>
       <c r="B11" t="n">
         <v>79946</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>411038</v>
+        <v>410994</v>
       </c>
       <c r="R11" t="n">
-        <v>6710225</v>
+        <v>6710184</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132197630</v>
+        <v>132197648</v>
       </c>
       <c r="B12" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410994</v>
+        <v>410933</v>
       </c>
       <c r="R12" t="n">
-        <v>6710184</v>
+        <v>6710072</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -5132,10 +5132,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132197627</v>
+        <v>132197668</v>
       </c>
       <c r="B47" t="n">
-        <v>79946</v>
+        <v>78993</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5143,21 +5143,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>410971</v>
+        <v>411097</v>
       </c>
       <c r="R47" t="n">
-        <v>6710196</v>
+        <v>6710289</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5229,7 +5229,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132197606</v>
+        <v>132197627</v>
       </c>
       <c r="B48" t="n">
         <v>79946</v>
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>410946</v>
+        <v>410971</v>
       </c>
       <c r="R48" t="n">
-        <v>6709981</v>
+        <v>6710196</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5326,10 +5326,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132197668</v>
+        <v>132197606</v>
       </c>
       <c r="B49" t="n">
-        <v>78993</v>
+        <v>79946</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5337,21 +5337,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5361,10 +5361,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>411097</v>
+        <v>410946</v>
       </c>
       <c r="R49" t="n">
-        <v>6710289</v>
+        <v>6709981</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>

--- a/artfynd/A 13525-2026 artfynd.xlsx
+++ b/artfynd/A 13525-2026 artfynd.xlsx
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132197663</v>
+        <v>132197619</v>
       </c>
       <c r="B8" t="n">
-        <v>78993</v>
+        <v>79947</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,21 +1358,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410929</v>
+        <v>411038</v>
       </c>
       <c r="R8" t="n">
-        <v>6710058</v>
+        <v>6710225</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1444,32 +1444,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132197640</v>
+        <v>132197630</v>
       </c>
       <c r="B9" t="n">
-        <v>79413</v>
+        <v>79947</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>410985</v>
+        <v>410994</v>
       </c>
       <c r="R9" t="n">
-        <v>6710205</v>
+        <v>6710184</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132197619</v>
+        <v>132197648</v>
       </c>
       <c r="B10" t="n">
-        <v>79946</v>
+        <v>79086</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>411038</v>
+        <v>410933</v>
       </c>
       <c r="R10" t="n">
-        <v>6710225</v>
+        <v>6710072</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1638,32 +1638,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132197630</v>
+        <v>132197640</v>
       </c>
       <c r="B11" t="n">
-        <v>79946</v>
+        <v>79414</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6450</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410994</v>
+        <v>410985</v>
       </c>
       <c r="R11" t="n">
-        <v>6710184</v>
+        <v>6710205</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132197648</v>
+        <v>132197663</v>
       </c>
       <c r="B12" t="n">
-        <v>79085</v>
+        <v>78994</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410933</v>
+        <v>410929</v>
       </c>
       <c r="R12" t="n">
-        <v>6710072</v>
+        <v>6710058</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1835,7 +1835,7 @@
         <v>132197669</v>
       </c>
       <c r="B13" t="n">
-        <v>78993</v>
+        <v>78994</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>132197666</v>
       </c>
       <c r="B14" t="n">
-        <v>78993</v>
+        <v>78994</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>132197601</v>
       </c>
       <c r="B15" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2123,32 +2123,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132197643</v>
+        <v>132197665</v>
       </c>
       <c r="B16" t="n">
-        <v>79351</v>
+        <v>78994</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>410998</v>
+        <v>410902</v>
       </c>
       <c r="R16" t="n">
         <v>6710163</v>
@@ -2220,32 +2220,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132197635</v>
+        <v>132197643</v>
       </c>
       <c r="B17" t="n">
-        <v>79946</v>
+        <v>79352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>410936</v>
+        <v>410998</v>
       </c>
       <c r="R17" t="n">
-        <v>6710017</v>
+        <v>6710163</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132197665</v>
+        <v>132197635</v>
       </c>
       <c r="B18" t="n">
-        <v>78993</v>
+        <v>79947</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>410902</v>
+        <v>410936</v>
       </c>
       <c r="R18" t="n">
-        <v>6710163</v>
+        <v>6710017</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2417,7 +2417,7 @@
         <v>132197670</v>
       </c>
       <c r="B19" t="n">
-        <v>78993</v>
+        <v>78994</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>132197671</v>
       </c>
       <c r="B20" t="n">
-        <v>78993</v>
+        <v>78994</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2608,10 +2608,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132197652</v>
+        <v>132197633</v>
       </c>
       <c r="B21" t="n">
-        <v>79085</v>
+        <v>79947</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,21 +2619,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>410937</v>
+        <v>410961</v>
       </c>
       <c r="R21" t="n">
-        <v>6710017</v>
+        <v>6710167</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2705,10 +2705,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132197651</v>
+        <v>132197631</v>
       </c>
       <c r="B22" t="n">
-        <v>79085</v>
+        <v>79947</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2716,21 +2716,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>411000</v>
+        <v>410991</v>
       </c>
       <c r="R22" t="n">
-        <v>6710007</v>
+        <v>6710191</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2802,10 +2802,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132197633</v>
+        <v>132197608</v>
       </c>
       <c r="B23" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410961</v>
+        <v>410931</v>
       </c>
       <c r="R23" t="n">
-        <v>6710167</v>
+        <v>6710096</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132197631</v>
+        <v>132197652</v>
       </c>
       <c r="B24" t="n">
-        <v>79946</v>
+        <v>79086</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2910,21 +2910,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410991</v>
+        <v>410937</v>
       </c>
       <c r="R24" t="n">
-        <v>6710191</v>
+        <v>6710017</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2996,10 +2996,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132197608</v>
+        <v>132197651</v>
       </c>
       <c r="B25" t="n">
-        <v>79946</v>
+        <v>79086</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3007,21 +3007,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410931</v>
+        <v>411000</v>
       </c>
       <c r="R25" t="n">
-        <v>6710096</v>
+        <v>6710007</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3093,10 +3093,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132197654</v>
+        <v>132197602</v>
       </c>
       <c r="B26" t="n">
-        <v>79084</v>
+        <v>79947</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3104,21 +3104,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410960</v>
+        <v>410973</v>
       </c>
       <c r="R26" t="n">
-        <v>6710167</v>
+        <v>6709995</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3190,10 +3190,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132197602</v>
+        <v>132197654</v>
       </c>
       <c r="B27" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3201,21 +3201,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>410973</v>
+        <v>410960</v>
       </c>
       <c r="R27" t="n">
-        <v>6709995</v>
+        <v>6710167</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3290,7 +3290,7 @@
         <v>132197644</v>
       </c>
       <c r="B28" t="n">
-        <v>79351</v>
+        <v>79352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>132197636</v>
       </c>
       <c r="B29" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>132197637</v>
       </c>
       <c r="B30" t="n">
-        <v>79917</v>
+        <v>79918</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>132197667</v>
       </c>
       <c r="B31" t="n">
-        <v>78993</v>
+        <v>78994</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132197605</v>
+        <v>132197615</v>
       </c>
       <c r="B32" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>410950</v>
+        <v>410939</v>
       </c>
       <c r="R32" t="n">
-        <v>6709984</v>
+        <v>6710183</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3772,10 +3772,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132197615</v>
+        <v>132197647</v>
       </c>
       <c r="B33" t="n">
-        <v>79946</v>
+        <v>79086</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3783,21 +3783,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>410939</v>
+        <v>410950</v>
       </c>
       <c r="R33" t="n">
-        <v>6710183</v>
+        <v>6709984</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3869,10 +3869,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132197647</v>
+        <v>132197605</v>
       </c>
       <c r="B34" t="n">
-        <v>79085</v>
+        <v>79947</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3880,21 +3880,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132197653</v>
+        <v>132197655</v>
       </c>
       <c r="B35" t="n">
-        <v>81312</v>
+        <v>79085</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3977,21 +3977,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>410972</v>
+        <v>411091</v>
       </c>
       <c r="R35" t="n">
-        <v>6710194</v>
+        <v>6710283</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4045,6 +4045,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4063,10 +4064,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132197659</v>
+        <v>132197653</v>
       </c>
       <c r="B36" t="n">
-        <v>78993</v>
+        <v>81313</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4074,21 +4075,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4098,10 +4099,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>410973</v>
+        <v>410972</v>
       </c>
       <c r="R36" t="n">
-        <v>6709994</v>
+        <v>6710194</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4142,7 +4143,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132197655</v>
+        <v>132197659</v>
       </c>
       <c r="B37" t="n">
-        <v>79084</v>
+        <v>78994</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>411091</v>
+        <v>410973</v>
       </c>
       <c r="R37" t="n">
-        <v>6710283</v>
+        <v>6709994</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4262,7 +4262,7 @@
         <v>132197646</v>
       </c>
       <c r="B38" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>132197650</v>
       </c>
       <c r="B39" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>132197618</v>
       </c>
       <c r="B40" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>132197632</v>
       </c>
       <c r="B41" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>132197634</v>
       </c>
       <c r="B42" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>132197600</v>
       </c>
       <c r="B43" t="n">
-        <v>78993</v>
+        <v>78994</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>132197609</v>
       </c>
       <c r="B44" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>132197656</v>
       </c>
       <c r="B45" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>132197662</v>
       </c>
       <c r="B46" t="n">
-        <v>78993</v>
+        <v>78994</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>132197668</v>
       </c>
       <c r="B47" t="n">
-        <v>78993</v>
+        <v>78994</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>132197627</v>
       </c>
       <c r="B48" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>132197606</v>
       </c>
       <c r="B49" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>132197629</v>
       </c>
       <c r="B50" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>132197628</v>
       </c>
       <c r="B51" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         <v>132197604</v>
       </c>
       <c r="B52" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>132197661</v>
       </c>
       <c r="B53" t="n">
-        <v>78993</v>
+        <v>78994</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>132197660</v>
       </c>
       <c r="B54" t="n">
-        <v>78993</v>
+        <v>78994</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>132197616</v>
       </c>
       <c r="B55" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6006,10 +6006,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132197664</v>
+        <v>132197607</v>
       </c>
       <c r="B56" t="n">
-        <v>78993</v>
+        <v>79947</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6017,21 +6017,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>410928</v>
+        <v>410933</v>
       </c>
       <c r="R56" t="n">
-        <v>6710090</v>
+        <v>6710072</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6103,10 +6103,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132197607</v>
+        <v>132197664</v>
       </c>
       <c r="B57" t="n">
-        <v>79946</v>
+        <v>78994</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6114,21 +6114,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6138,10 +6138,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>410933</v>
+        <v>410928</v>
       </c>
       <c r="R57" t="n">
-        <v>6710072</v>
+        <v>6710090</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>

--- a/artfynd/A 13525-2026 artfynd.xlsx
+++ b/artfynd/A 13525-2026 artfynd.xlsx
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132197619</v>
+        <v>132197663</v>
       </c>
       <c r="B8" t="n">
-        <v>79947</v>
+        <v>78994</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,21 +1358,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>411038</v>
+        <v>410929</v>
       </c>
       <c r="R8" t="n">
-        <v>6710225</v>
+        <v>6710058</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1444,32 +1444,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132197630</v>
+        <v>132197640</v>
       </c>
       <c r="B9" t="n">
-        <v>79947</v>
+        <v>79414</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6450</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>410994</v>
+        <v>410985</v>
       </c>
       <c r="R9" t="n">
-        <v>6710184</v>
+        <v>6710205</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132197648</v>
+        <v>132197619</v>
       </c>
       <c r="B10" t="n">
-        <v>79086</v>
+        <v>79947</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>410933</v>
+        <v>411038</v>
       </c>
       <c r="R10" t="n">
-        <v>6710072</v>
+        <v>6710225</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1638,32 +1638,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132197640</v>
+        <v>132197630</v>
       </c>
       <c r="B11" t="n">
-        <v>79414</v>
+        <v>79947</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410985</v>
+        <v>410994</v>
       </c>
       <c r="R11" t="n">
-        <v>6710205</v>
+        <v>6710184</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132197663</v>
+        <v>132197648</v>
       </c>
       <c r="B12" t="n">
-        <v>78994</v>
+        <v>79086</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410929</v>
+        <v>410933</v>
       </c>
       <c r="R12" t="n">
-        <v>6710058</v>
+        <v>6710072</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -3093,10 +3093,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132197602</v>
+        <v>132197654</v>
       </c>
       <c r="B26" t="n">
-        <v>79947</v>
+        <v>79085</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3104,21 +3104,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410973</v>
+        <v>410960</v>
       </c>
       <c r="R26" t="n">
-        <v>6709995</v>
+        <v>6710167</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3190,10 +3190,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132197654</v>
+        <v>132197602</v>
       </c>
       <c r="B27" t="n">
-        <v>79085</v>
+        <v>79947</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3201,21 +3201,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>410960</v>
+        <v>410973</v>
       </c>
       <c r="R27" t="n">
-        <v>6710167</v>
+        <v>6709995</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132197667</v>
+        <v>132197605</v>
       </c>
       <c r="B31" t="n">
-        <v>78994</v>
+        <v>79947</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>411027</v>
+        <v>410950</v>
       </c>
       <c r="R31" t="n">
-        <v>6710222</v>
+        <v>6709984</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3869,10 +3869,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132197605</v>
+        <v>132197667</v>
       </c>
       <c r="B34" t="n">
-        <v>79947</v>
+        <v>78994</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3880,21 +3880,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>410950</v>
+        <v>411027</v>
       </c>
       <c r="R34" t="n">
-        <v>6709984</v>
+        <v>6710222</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132197655</v>
+        <v>132197646</v>
       </c>
       <c r="B35" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3977,21 +3977,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>411091</v>
+        <v>410983</v>
       </c>
       <c r="R35" t="n">
-        <v>6710283</v>
+        <v>6709997</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4045,7 +4045,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4064,10 +4063,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132197653</v>
+        <v>132197650</v>
       </c>
       <c r="B36" t="n">
-        <v>81313</v>
+        <v>79086</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,21 +4074,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4099,10 +4098,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>410972</v>
+        <v>410986</v>
       </c>
       <c r="R36" t="n">
-        <v>6710194</v>
+        <v>6710178</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4161,10 +4160,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132197659</v>
+        <v>132197653</v>
       </c>
       <c r="B37" t="n">
-        <v>78994</v>
+        <v>81313</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4172,21 +4171,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4196,10 +4195,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>410973</v>
+        <v>410972</v>
       </c>
       <c r="R37" t="n">
-        <v>6709994</v>
+        <v>6710194</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4240,7 +4239,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4259,10 +4257,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132197646</v>
+        <v>132197655</v>
       </c>
       <c r="B38" t="n">
-        <v>79086</v>
+        <v>79085</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4270,21 +4268,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4294,10 +4292,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>410983</v>
+        <v>411091</v>
       </c>
       <c r="R38" t="n">
-        <v>6709997</v>
+        <v>6710283</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4338,6 +4336,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4356,10 +4355,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132197650</v>
+        <v>132197659</v>
       </c>
       <c r="B39" t="n">
-        <v>79086</v>
+        <v>78994</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4367,21 +4366,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4391,10 +4390,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>410986</v>
+        <v>410973</v>
       </c>
       <c r="R39" t="n">
-        <v>6710178</v>
+        <v>6709994</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4435,6 +4434,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4550,7 +4550,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132197632</v>
+        <v>132197634</v>
       </c>
       <c r="B41" t="n">
         <v>79947</v>
@@ -4585,10 +4585,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>410998</v>
+        <v>410980</v>
       </c>
       <c r="R41" t="n">
-        <v>6710163</v>
+        <v>6710008</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4647,7 +4647,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132197634</v>
+        <v>132197632</v>
       </c>
       <c r="B42" t="n">
         <v>79947</v>
@@ -4682,10 +4682,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>410980</v>
+        <v>410998</v>
       </c>
       <c r="R42" t="n">
-        <v>6710008</v>
+        <v>6710163</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4744,10 +4744,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132197600</v>
+        <v>132197609</v>
       </c>
       <c r="B43" t="n">
-        <v>78994</v>
+        <v>79947</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4755,21 +4755,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>410935</v>
+        <v>410902</v>
       </c>
       <c r="R43" t="n">
-        <v>6710081</v>
+        <v>6710163</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4841,10 +4841,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132197609</v>
+        <v>132197656</v>
       </c>
       <c r="B44" t="n">
-        <v>79947</v>
+        <v>79328</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4852,21 +4852,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4876,10 +4876,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>410902</v>
+        <v>410938</v>
       </c>
       <c r="R44" t="n">
-        <v>6710163</v>
+        <v>6710077</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4938,10 +4938,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132197656</v>
+        <v>132197600</v>
       </c>
       <c r="B45" t="n">
-        <v>79328</v>
+        <v>78994</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4949,21 +4949,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>410938</v>
+        <v>410935</v>
       </c>
       <c r="R45" t="n">
-        <v>6710077</v>
+        <v>6710081</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5132,10 +5132,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132197668</v>
+        <v>132197627</v>
       </c>
       <c r="B47" t="n">
-        <v>78994</v>
+        <v>79947</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5143,21 +5143,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>411097</v>
+        <v>410971</v>
       </c>
       <c r="R47" t="n">
-        <v>6710289</v>
+        <v>6710196</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5229,7 +5229,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132197627</v>
+        <v>132197606</v>
       </c>
       <c r="B48" t="n">
         <v>79947</v>
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>410971</v>
+        <v>410946</v>
       </c>
       <c r="R48" t="n">
-        <v>6710196</v>
+        <v>6709981</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5326,10 +5326,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132197606</v>
+        <v>132197668</v>
       </c>
       <c r="B49" t="n">
-        <v>79947</v>
+        <v>78994</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5337,21 +5337,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5361,10 +5361,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>410946</v>
+        <v>411097</v>
       </c>
       <c r="R49" t="n">
-        <v>6709981</v>
+        <v>6710289</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5811,10 +5811,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132197660</v>
+        <v>132197616</v>
       </c>
       <c r="B54" t="n">
-        <v>78994</v>
+        <v>79947</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5822,21 +5822,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>410994</v>
+        <v>410952</v>
       </c>
       <c r="R54" t="n">
-        <v>6710185</v>
+        <v>6710170</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5890,7 +5890,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5909,10 +5908,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132197616</v>
+        <v>132197660</v>
       </c>
       <c r="B55" t="n">
-        <v>79947</v>
+        <v>78994</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5920,21 +5919,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5944,10 +5943,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>410952</v>
+        <v>410994</v>
       </c>
       <c r="R55" t="n">
-        <v>6710170</v>
+        <v>6710185</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5988,6 +5987,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13525-2026 artfynd.xlsx
+++ b/artfynd/A 13525-2026 artfynd.xlsx
@@ -1350,7 +1350,7 @@
         <v>132197663</v>
       </c>
       <c r="B8" t="n">
-        <v>78994</v>
+        <v>78995</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>132197640</v>
       </c>
       <c r="B9" t="n">
-        <v>79414</v>
+        <v>79415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>132197619</v>
       </c>
       <c r="B10" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>132197630</v>
       </c>
       <c r="B11" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>132197648</v>
       </c>
       <c r="B12" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>132197669</v>
       </c>
       <c r="B13" t="n">
-        <v>78994</v>
+        <v>78995</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>132197666</v>
       </c>
       <c r="B14" t="n">
-        <v>78994</v>
+        <v>78995</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>132197601</v>
       </c>
       <c r="B15" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>132197665</v>
       </c>
       <c r="B16" t="n">
-        <v>78994</v>
+        <v>78995</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>132197643</v>
       </c>
       <c r="B17" t="n">
-        <v>79352</v>
+        <v>79353</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>132197635</v>
       </c>
       <c r="B18" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>132197670</v>
       </c>
       <c r="B19" t="n">
-        <v>78994</v>
+        <v>78995</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>132197671</v>
       </c>
       <c r="B20" t="n">
-        <v>78994</v>
+        <v>78995</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>132197633</v>
       </c>
       <c r="B21" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>132197631</v>
       </c>
       <c r="B22" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>132197608</v>
       </c>
       <c r="B23" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>132197652</v>
       </c>
       <c r="B24" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>132197651</v>
       </c>
       <c r="B25" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>132197654</v>
       </c>
       <c r="B26" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>132197602</v>
       </c>
       <c r="B27" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>132197644</v>
       </c>
       <c r="B28" t="n">
-        <v>79352</v>
+        <v>79353</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>132197636</v>
       </c>
       <c r="B29" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>132197637</v>
       </c>
       <c r="B30" t="n">
-        <v>79918</v>
+        <v>79919</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132197605</v>
+        <v>132197647</v>
       </c>
       <c r="B31" t="n">
-        <v>79947</v>
+        <v>79087</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132197615</v>
+        <v>132197667</v>
       </c>
       <c r="B32" t="n">
-        <v>79947</v>
+        <v>78995</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3686,21 +3686,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>410939</v>
+        <v>411027</v>
       </c>
       <c r="R32" t="n">
-        <v>6710183</v>
+        <v>6710222</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3772,10 +3772,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132197647</v>
+        <v>132197605</v>
       </c>
       <c r="B33" t="n">
-        <v>79086</v>
+        <v>79948</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3783,21 +3783,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3869,10 +3869,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132197667</v>
+        <v>132197615</v>
       </c>
       <c r="B34" t="n">
-        <v>78994</v>
+        <v>79948</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3880,21 +3880,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>411027</v>
+        <v>410939</v>
       </c>
       <c r="R34" t="n">
-        <v>6710222</v>
+        <v>6710183</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3969,7 +3969,7 @@
         <v>132197646</v>
       </c>
       <c r="B35" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>132197650</v>
       </c>
       <c r="B36" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4160,10 +4160,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132197653</v>
+        <v>132197659</v>
       </c>
       <c r="B37" t="n">
-        <v>81313</v>
+        <v>78995</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4171,21 +4171,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4195,10 +4195,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>410972</v>
+        <v>410973</v>
       </c>
       <c r="R37" t="n">
-        <v>6710194</v>
+        <v>6709994</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4239,6 +4239,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4260,7 +4261,7 @@
         <v>132197655</v>
       </c>
       <c r="B38" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4355,10 +4356,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132197659</v>
+        <v>132197653</v>
       </c>
       <c r="B39" t="n">
-        <v>78994</v>
+        <v>81314</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4366,21 +4367,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4390,10 +4391,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>410973</v>
+        <v>410972</v>
       </c>
       <c r="R39" t="n">
-        <v>6709994</v>
+        <v>6710194</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4434,7 +4435,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4456,7 +4456,7 @@
         <v>132197618</v>
       </c>
       <c r="B40" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4550,10 +4550,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132197634</v>
+        <v>132197632</v>
       </c>
       <c r="B41" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4585,10 +4585,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>410980</v>
+        <v>410998</v>
       </c>
       <c r="R41" t="n">
-        <v>6710008</v>
+        <v>6710163</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4647,10 +4647,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132197632</v>
+        <v>132197634</v>
       </c>
       <c r="B42" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4682,10 +4682,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>410998</v>
+        <v>410980</v>
       </c>
       <c r="R42" t="n">
-        <v>6710163</v>
+        <v>6710008</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4744,10 +4744,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132197609</v>
+        <v>132197600</v>
       </c>
       <c r="B43" t="n">
-        <v>79947</v>
+        <v>78995</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4755,21 +4755,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>410902</v>
+        <v>410935</v>
       </c>
       <c r="R43" t="n">
-        <v>6710163</v>
+        <v>6710081</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4841,10 +4841,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132197656</v>
+        <v>132197609</v>
       </c>
       <c r="B44" t="n">
-        <v>79328</v>
+        <v>79948</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4852,21 +4852,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4876,10 +4876,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>410938</v>
+        <v>410902</v>
       </c>
       <c r="R44" t="n">
-        <v>6710077</v>
+        <v>6710163</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4938,10 +4938,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132197600</v>
+        <v>132197656</v>
       </c>
       <c r="B45" t="n">
-        <v>78994</v>
+        <v>79329</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4949,21 +4949,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>410935</v>
+        <v>410938</v>
       </c>
       <c r="R45" t="n">
-        <v>6710081</v>
+        <v>6710077</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5038,7 +5038,7 @@
         <v>132197662</v>
       </c>
       <c r="B46" t="n">
-        <v>78994</v>
+        <v>78995</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>132197627</v>
       </c>
       <c r="B47" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>132197606</v>
       </c>
       <c r="B48" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>132197668</v>
       </c>
       <c r="B49" t="n">
-        <v>78994</v>
+        <v>78995</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>132197629</v>
       </c>
       <c r="B50" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>132197628</v>
       </c>
       <c r="B51" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         <v>132197604</v>
       </c>
       <c r="B52" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>132197661</v>
       </c>
       <c r="B53" t="n">
-        <v>78994</v>
+        <v>78995</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5811,10 +5811,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132197616</v>
+        <v>132197660</v>
       </c>
       <c r="B54" t="n">
-        <v>79947</v>
+        <v>78995</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5822,21 +5822,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>410952</v>
+        <v>410994</v>
       </c>
       <c r="R54" t="n">
-        <v>6710170</v>
+        <v>6710185</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5890,6 +5890,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5908,10 +5909,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132197660</v>
+        <v>132197616</v>
       </c>
       <c r="B55" t="n">
-        <v>78994</v>
+        <v>79948</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5919,21 +5920,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5943,10 +5944,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>410994</v>
+        <v>410952</v>
       </c>
       <c r="R55" t="n">
-        <v>6710185</v>
+        <v>6710170</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5987,7 +5988,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6009,7 +6009,7 @@
         <v>132197607</v>
       </c>
       <c r="B56" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>132197664</v>
       </c>
       <c r="B57" t="n">
-        <v>78994</v>
+        <v>78995</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 13525-2026 artfynd.xlsx
+++ b/artfynd/A 13525-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102127508</v>
+        <v>102127465</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>410919.3226665345</v>
+        <v>410939</v>
       </c>
       <c r="R2" t="n">
-        <v>6710006.014335259</v>
+        <v>6709973</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-07-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102127458</v>
+        <v>132197600</v>
       </c>
       <c r="B3" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Navarbäcksmyren, Vrm</t>
+          <t>Söder om Römosstjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>410938.7642541217</v>
+        <v>410935</v>
       </c>
       <c r="R3" t="n">
-        <v>6709974.006810497</v>
+        <v>6710081</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102127465</v>
+        <v>132197659</v>
       </c>
       <c r="B4" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,17 +900,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Navarbäcksmyren, Vrm</t>
+          <t>Söder om Römosstjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>410938.739980302</v>
+        <v>410973</v>
       </c>
       <c r="R4" t="n">
-        <v>6709973.02214841</v>
+        <v>6709994</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,33 +948,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102127504</v>
+        <v>132197660</v>
       </c>
       <c r="B5" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,37 +978,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Navarbäcksmyren, Vrm</t>
+          <t>Söder om Römosstjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>410934.0028326925</v>
+        <v>410994</v>
       </c>
       <c r="R5" t="n">
-        <v>6709981.021008047</v>
+        <v>6710185</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1032,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,33 +1046,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102126327</v>
+        <v>132197661</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,37 +1076,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Navarbäcksmyren, Vrm</t>
+          <t>Söder om Römosstjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>410957.0345095119</v>
+        <v>410984</v>
       </c>
       <c r="R6" t="n">
-        <v>6709974.541719727</v>
+        <v>6709996</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,22 +1130,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,27 +1150,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102126321</v>
+        <v>132197662</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,37 +1173,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Navarbäcksmyren, Vrm</t>
+          <t>Söder om Römosstjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>410950.9591356653</v>
+        <v>410939</v>
       </c>
       <c r="R7" t="n">
-        <v>6709968.287268362</v>
+        <v>6710046</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,22 +1227,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,44 +1247,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132197640</v>
+        <v>132197663</v>
       </c>
       <c r="B8" t="n">
-        <v>79415</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6450</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1294,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410985</v>
+        <v>410929</v>
       </c>
       <c r="R8" t="n">
-        <v>6710205</v>
+        <v>6710058</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1444,10 +1356,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132197619</v>
+        <v>132197664</v>
       </c>
       <c r="B9" t="n">
-        <v>79948</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,21 +1367,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1391,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>411038</v>
+        <v>410928</v>
       </c>
       <c r="R9" t="n">
-        <v>6710225</v>
+        <v>6710090</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,10 +1453,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132197630</v>
+        <v>132197665</v>
       </c>
       <c r="B10" t="n">
-        <v>79948</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,21 +1464,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1488,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>410994</v>
+        <v>410902</v>
       </c>
       <c r="R10" t="n">
-        <v>6710184</v>
+        <v>6710163</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1638,10 +1550,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132197648</v>
+        <v>132197666</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1561,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1585,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410933</v>
+        <v>410952</v>
       </c>
       <c r="R11" t="n">
-        <v>6710072</v>
+        <v>6710169</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1735,10 +1647,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132197663</v>
+        <v>132197667</v>
       </c>
       <c r="B12" t="n">
-        <v>78995</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,10 +1682,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410929</v>
+        <v>411027</v>
       </c>
       <c r="R12" t="n">
-        <v>6710058</v>
+        <v>6710222</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1832,10 +1744,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132197601</v>
+        <v>132197668</v>
       </c>
       <c r="B13" t="n">
-        <v>79948</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,21 +1755,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1779,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>410984</v>
+        <v>411097</v>
       </c>
       <c r="R13" t="n">
-        <v>6709997</v>
+        <v>6710289</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1932,7 +1844,7 @@
         <v>132197669</v>
       </c>
       <c r="B14" t="n">
-        <v>78995</v>
+        <v>79039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2026,10 +1938,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132197666</v>
+        <v>132197670</v>
       </c>
       <c r="B15" t="n">
-        <v>78995</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,10 +1973,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>410952</v>
+        <v>410995</v>
       </c>
       <c r="R15" t="n">
-        <v>6710169</v>
+        <v>6710181</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2123,32 +2035,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132197643</v>
+        <v>132197671</v>
       </c>
       <c r="B16" t="n">
-        <v>79353</v>
+        <v>79039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2070,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>410998</v>
+        <v>410977</v>
       </c>
       <c r="R16" t="n">
-        <v>6710163</v>
+        <v>6710177</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2220,10 +2132,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132197635</v>
+        <v>132197653</v>
       </c>
       <c r="B17" t="n">
-        <v>79948</v>
+        <v>81355</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2231,21 +2143,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2167,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>410936</v>
+        <v>410972</v>
       </c>
       <c r="R17" t="n">
-        <v>6710017</v>
+        <v>6710194</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2317,48 +2229,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132197665</v>
+        <v>102126321</v>
       </c>
       <c r="B18" t="n">
-        <v>78995</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Söder om Römosstjärnen, Vrm</t>
+          <t>Navarbäcksmyren, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>410902</v>
+        <v>410951</v>
       </c>
       <c r="R18" t="n">
-        <v>6710163</v>
+        <v>6709968</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2382,12 +2294,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2402,60 +2314,60 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132197670</v>
+        <v>102126327</v>
       </c>
       <c r="B19" t="n">
-        <v>78995</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Söder om Römosstjärnen, Vrm</t>
+          <t>Navarbäcksmyren, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>410995</v>
+        <v>410957</v>
       </c>
       <c r="R19" t="n">
-        <v>6710181</v>
+        <v>6709974</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2479,12 +2391,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2499,60 +2411,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132197671</v>
+        <v>102127508</v>
       </c>
       <c r="B20" t="n">
-        <v>78995</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Söder om Römosstjärnen, Vrm</t>
+          <t>Navarbäcksmyren, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>410977</v>
+        <v>410920</v>
       </c>
       <c r="R20" t="n">
-        <v>6710177</v>
+        <v>6710006</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2576,12 +2488,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2596,44 +2508,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132197652</v>
+        <v>132197656</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2643,10 +2555,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>410937</v>
+        <v>410938</v>
       </c>
       <c r="R21" t="n">
-        <v>6710017</v>
+        <v>6710077</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2705,32 +2617,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132197651</v>
+        <v>132197641</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>79397</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2740,10 +2652,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>411000</v>
+        <v>410906</v>
       </c>
       <c r="R22" t="n">
-        <v>6710007</v>
+        <v>6710194</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2802,32 +2714,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132197633</v>
+        <v>132197642</v>
       </c>
       <c r="B23" t="n">
-        <v>79948</v>
+        <v>79397</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2837,10 +2749,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410961</v>
+        <v>410998</v>
       </c>
       <c r="R23" t="n">
-        <v>6710167</v>
+        <v>6710231</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2899,32 +2811,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132197631</v>
+        <v>132197643</v>
       </c>
       <c r="B24" t="n">
-        <v>79948</v>
+        <v>79397</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2934,10 +2846,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410991</v>
+        <v>410998</v>
       </c>
       <c r="R24" t="n">
-        <v>6710191</v>
+        <v>6710163</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2996,32 +2908,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132197608</v>
+        <v>132197644</v>
       </c>
       <c r="B25" t="n">
-        <v>79948</v>
+        <v>79397</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3031,10 +2943,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410931</v>
+        <v>410908</v>
       </c>
       <c r="R25" t="n">
-        <v>6710096</v>
+        <v>6710026</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3096,7 +3008,7 @@
         <v>132197654</v>
       </c>
       <c r="B26" t="n">
-        <v>79086</v>
+        <v>79130</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3190,10 +3102,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132197602</v>
+        <v>132197655</v>
       </c>
       <c r="B27" t="n">
-        <v>79948</v>
+        <v>79130</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3201,21 +3113,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3225,10 +3137,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>410973</v>
+        <v>411091</v>
       </c>
       <c r="R27" t="n">
-        <v>6709995</v>
+        <v>6710283</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3269,6 +3181,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3287,32 +3200,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132197644</v>
+        <v>132197640</v>
       </c>
       <c r="B28" t="n">
-        <v>79353</v>
+        <v>79459</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6434</v>
+        <v>6450</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3322,10 +3235,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>410908</v>
+        <v>410985</v>
       </c>
       <c r="R28" t="n">
-        <v>6710026</v>
+        <v>6710205</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3384,10 +3297,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132197636</v>
+        <v>102127504</v>
       </c>
       <c r="B29" t="n">
-        <v>79948</v>
+        <v>79946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3415,17 +3328,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Söder om Römosstjärnen, Vrm</t>
+          <t>Navarbäcksmyren, Vrm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>410907</v>
+        <v>410934</v>
       </c>
       <c r="R29" t="n">
-        <v>6710026</v>
+        <v>6709981</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3449,12 +3362,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3469,22 +3382,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132197637</v>
+        <v>132197601</v>
       </c>
       <c r="B30" t="n">
-        <v>79919</v>
+        <v>79992</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3492,21 +3405,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3516,10 +3429,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>410906</v>
+        <v>410984</v>
       </c>
       <c r="R30" t="n">
-        <v>6710027</v>
+        <v>6709997</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3578,10 +3491,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132197667</v>
+        <v>132197602</v>
       </c>
       <c r="B31" t="n">
-        <v>78995</v>
+        <v>79992</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3589,21 +3502,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3526,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>411027</v>
+        <v>410973</v>
       </c>
       <c r="R31" t="n">
-        <v>6710222</v>
+        <v>6709995</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3675,10 +3588,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132197647</v>
+        <v>132197604</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>79992</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3686,21 +3599,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3710,10 +3623,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>410950</v>
+        <v>410959</v>
       </c>
       <c r="R32" t="n">
-        <v>6709984</v>
+        <v>6709986</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3775,7 +3688,7 @@
         <v>132197605</v>
       </c>
       <c r="B33" t="n">
-        <v>79948</v>
+        <v>79992</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3869,10 +3782,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132197615</v>
+        <v>132197606</v>
       </c>
       <c r="B34" t="n">
-        <v>79948</v>
+        <v>79992</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3904,10 +3817,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>410939</v>
+        <v>410946</v>
       </c>
       <c r="R34" t="n">
-        <v>6710183</v>
+        <v>6709981</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3966,10 +3879,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132197655</v>
+        <v>132197607</v>
       </c>
       <c r="B35" t="n">
-        <v>79086</v>
+        <v>79992</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3977,21 +3890,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4001,10 +3914,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>411091</v>
+        <v>410933</v>
       </c>
       <c r="R35" t="n">
-        <v>6710283</v>
+        <v>6710072</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4045,7 +3958,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4064,10 +3976,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132197653</v>
+        <v>132197608</v>
       </c>
       <c r="B36" t="n">
-        <v>81314</v>
+        <v>79992</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,21 +3987,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4099,10 +4011,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>410972</v>
+        <v>410931</v>
       </c>
       <c r="R36" t="n">
-        <v>6710194</v>
+        <v>6710096</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4161,10 +4073,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132197659</v>
+        <v>132197609</v>
       </c>
       <c r="B37" t="n">
-        <v>78995</v>
+        <v>79992</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4172,21 +4084,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4196,10 +4108,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>410973</v>
+        <v>410902</v>
       </c>
       <c r="R37" t="n">
-        <v>6709994</v>
+        <v>6710163</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4240,7 +4152,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4259,10 +4170,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132197646</v>
+        <v>132197611</v>
       </c>
       <c r="B38" t="n">
-        <v>79087</v>
+        <v>79992</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4270,21 +4181,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4294,10 +4205,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>410983</v>
+        <v>410907</v>
       </c>
       <c r="R38" t="n">
-        <v>6709997</v>
+        <v>6710193</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4356,10 +4267,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132197650</v>
+        <v>132197612</v>
       </c>
       <c r="B39" t="n">
-        <v>79087</v>
+        <v>79992</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4367,21 +4278,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4391,10 +4302,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>410986</v>
+        <v>410905</v>
       </c>
       <c r="R39" t="n">
-        <v>6710178</v>
+        <v>6710193</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4453,10 +4364,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132197618</v>
+        <v>132197613</v>
       </c>
       <c r="B40" t="n">
-        <v>79948</v>
+        <v>79992</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4488,10 +4399,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>411027</v>
+        <v>410929</v>
       </c>
       <c r="R40" t="n">
-        <v>6710222</v>
+        <v>6710183</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4550,10 +4461,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132197632</v>
+        <v>132197614</v>
       </c>
       <c r="B41" t="n">
-        <v>79948</v>
+        <v>79992</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4585,10 +4496,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>410998</v>
+        <v>410924</v>
       </c>
       <c r="R41" t="n">
-        <v>6710163</v>
+        <v>6710182</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4647,10 +4558,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132197634</v>
+        <v>132197615</v>
       </c>
       <c r="B42" t="n">
-        <v>79948</v>
+        <v>79992</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4682,10 +4593,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>410980</v>
+        <v>410939</v>
       </c>
       <c r="R42" t="n">
-        <v>6710008</v>
+        <v>6710183</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4744,10 +4655,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132197609</v>
+        <v>132197616</v>
       </c>
       <c r="B43" t="n">
-        <v>79948</v>
+        <v>79992</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4779,10 +4690,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>410902</v>
+        <v>410952</v>
       </c>
       <c r="R43" t="n">
-        <v>6710163</v>
+        <v>6710170</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4841,10 +4752,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132197656</v>
+        <v>132197617</v>
       </c>
       <c r="B44" t="n">
-        <v>79329</v>
+        <v>79992</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4852,21 +4763,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4876,10 +4787,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>410938</v>
+        <v>411027</v>
       </c>
       <c r="R44" t="n">
-        <v>6710077</v>
+        <v>6710222</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4938,10 +4849,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132197600</v>
+        <v>132197619</v>
       </c>
       <c r="B45" t="n">
-        <v>78995</v>
+        <v>79992</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4949,21 +4860,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4973,10 +4884,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>410935</v>
+        <v>411038</v>
       </c>
       <c r="R45" t="n">
-        <v>6710081</v>
+        <v>6710225</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5035,10 +4946,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132197662</v>
+        <v>132197623</v>
       </c>
       <c r="B46" t="n">
-        <v>78995</v>
+        <v>79992</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5046,21 +4957,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5070,10 +4981,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>410939</v>
+        <v>411029</v>
       </c>
       <c r="R46" t="n">
-        <v>6710046</v>
+        <v>6710256</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5132,10 +5043,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132197627</v>
+        <v>132197625</v>
       </c>
       <c r="B47" t="n">
-        <v>79948</v>
+        <v>79992</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5167,10 +5078,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>410971</v>
+        <v>410998</v>
       </c>
       <c r="R47" t="n">
-        <v>6710196</v>
+        <v>6710232</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5229,10 +5140,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132197606</v>
+        <v>132197626</v>
       </c>
       <c r="B48" t="n">
-        <v>79948</v>
+        <v>79992</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5264,10 +5175,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>410946</v>
+        <v>410995</v>
       </c>
       <c r="R48" t="n">
-        <v>6709981</v>
+        <v>6710237</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5326,10 +5237,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132197668</v>
+        <v>132197627</v>
       </c>
       <c r="B49" t="n">
-        <v>78995</v>
+        <v>79992</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5337,21 +5248,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5361,10 +5272,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>411097</v>
+        <v>410971</v>
       </c>
       <c r="R49" t="n">
-        <v>6710289</v>
+        <v>6710196</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5423,10 +5334,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132197629</v>
+        <v>132197628</v>
       </c>
       <c r="B50" t="n">
-        <v>79948</v>
+        <v>79992</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5458,10 +5369,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>410993</v>
+        <v>410998</v>
       </c>
       <c r="R50" t="n">
-        <v>6710175</v>
+        <v>6710174</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5520,10 +5431,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132197628</v>
+        <v>132197629</v>
       </c>
       <c r="B51" t="n">
-        <v>79948</v>
+        <v>79992</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5555,10 +5466,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>410998</v>
+        <v>410993</v>
       </c>
       <c r="R51" t="n">
-        <v>6710174</v>
+        <v>6710175</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5617,10 +5528,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132197604</v>
+        <v>132197630</v>
       </c>
       <c r="B52" t="n">
-        <v>79948</v>
+        <v>79992</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5652,10 +5563,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>410959</v>
+        <v>410994</v>
       </c>
       <c r="R52" t="n">
-        <v>6709986</v>
+        <v>6710184</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5714,10 +5625,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132197661</v>
+        <v>132197631</v>
       </c>
       <c r="B53" t="n">
-        <v>78995</v>
+        <v>79992</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5725,21 +5636,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5749,10 +5660,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>410984</v>
+        <v>410991</v>
       </c>
       <c r="R53" t="n">
-        <v>6709996</v>
+        <v>6710191</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5811,10 +5722,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132197616</v>
+        <v>132197632</v>
       </c>
       <c r="B54" t="n">
-        <v>79948</v>
+        <v>79992</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5846,10 +5757,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>410952</v>
+        <v>410998</v>
       </c>
       <c r="R54" t="n">
-        <v>6710170</v>
+        <v>6710163</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5908,10 +5819,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132197660</v>
+        <v>132197633</v>
       </c>
       <c r="B55" t="n">
-        <v>78995</v>
+        <v>79992</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5919,21 +5830,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5943,10 +5854,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>410994</v>
+        <v>410961</v>
       </c>
       <c r="R55" t="n">
-        <v>6710185</v>
+        <v>6710167</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5987,7 +5898,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6006,10 +5916,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132197607</v>
+        <v>132197634</v>
       </c>
       <c r="B56" t="n">
-        <v>79948</v>
+        <v>79992</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6041,10 +5951,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>410933</v>
+        <v>410980</v>
       </c>
       <c r="R56" t="n">
-        <v>6710072</v>
+        <v>6710008</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6103,10 +6013,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132197664</v>
+        <v>132197635</v>
       </c>
       <c r="B57" t="n">
-        <v>78995</v>
+        <v>79992</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6114,21 +6024,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6138,10 +6048,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>410928</v>
+        <v>410936</v>
       </c>
       <c r="R57" t="n">
-        <v>6710090</v>
+        <v>6710017</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6197,6 +6107,976 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>132197636</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>410907</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6710026</v>
+      </c>
+      <c r="S58" t="n">
+        <v>25</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>102127458</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Navarbäcksmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>410939</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6709974</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2022-07-07</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2022-07-07</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>132197646</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>410983</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6709997</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>132197647</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>410950</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6709984</v>
+      </c>
+      <c r="S61" t="n">
+        <v>25</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>132197648</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>410933</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6710072</v>
+      </c>
+      <c r="S62" t="n">
+        <v>25</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>132197649</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>410993</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6710236</v>
+      </c>
+      <c r="S63" t="n">
+        <v>25</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>132197650</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>410986</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6710178</v>
+      </c>
+      <c r="S64" t="n">
+        <v>25</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>132197651</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>411000</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6710007</v>
+      </c>
+      <c r="S65" t="n">
+        <v>25</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>132197652</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>410937</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6710017</v>
+      </c>
+      <c r="S66" t="n">
+        <v>25</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>132197637</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Söder om Römosstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>410906</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6710027</v>
+      </c>
+      <c r="S67" t="n">
+        <v>25</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13525-2026 artfynd.xlsx
+++ b/artfynd/A 13525-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AZ67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102127465</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197600</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197659</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1062,6 +1082,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197660</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1159,6 +1184,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197661</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1256,6 +1286,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197662</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1353,6 +1388,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197663</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1450,6 +1490,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197664</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1547,6 +1592,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197665</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1644,6 +1694,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197666</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1741,6 +1796,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197667</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1838,6 +1898,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197668</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1935,6 +2000,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197669</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2032,6 +2102,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197670</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2129,6 +2204,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197671</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2226,6 +2306,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197653</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2323,6 +2408,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102126321</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2420,6 +2510,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102126327</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2517,6 +2612,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102127508</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2614,6 +2714,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197656</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2711,6 +2816,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197641</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2808,6 +2918,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197642</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2905,6 +3020,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197643</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3002,6 +3122,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197644</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3099,6 +3224,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197654</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3197,6 +3327,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197655</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3294,6 +3429,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197640</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3391,6 +3531,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102127504</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3488,6 +3633,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197601</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3585,6 +3735,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197602</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3682,6 +3837,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197604</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3779,6 +3939,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197605</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3876,6 +4041,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197606</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3973,6 +4143,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197607</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4070,6 +4245,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197608</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4167,6 +4347,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197609</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4264,6 +4449,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197611</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4361,6 +4551,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197612</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4458,6 +4653,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197613</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4555,6 +4755,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197614</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4652,6 +4857,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197615</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4749,6 +4959,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197616</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4846,6 +5061,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197617</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4943,6 +5163,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197619</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5040,6 +5265,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197623</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5137,6 +5367,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197625</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5234,6 +5469,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197626</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5331,6 +5571,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197627</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5428,6 +5673,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197628</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5525,6 +5775,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197629</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5622,6 +5877,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197630</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5719,6 +5979,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197631</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5816,6 +6081,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197632</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5913,6 +6183,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197633</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6010,6 +6285,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197634</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6107,6 +6387,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197635</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6204,6 +6489,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197636</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6301,6 +6591,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102127458</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6398,6 +6693,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197646</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6495,6 +6795,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197647</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6592,6 +6897,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197648</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6689,6 +6999,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197649</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6786,6 +7101,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197650</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6883,6 +7203,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197651</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6980,6 +7305,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197652</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7077,8 +7407,81 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197637</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>